--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41252E3D-B18E-45FB-8CD3-5272A1BDFFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793AADE0-1806-49EC-906F-A4BBAEE3F6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="25년 1회" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>문제</t>
   </si>
@@ -315,6 +314,23 @@
   <si>
     <t>2.61[V]</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250104(1), 250104(2),</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250106a</t>
+  </si>
+  <si>
+    <t>250107a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250117a</t>
+  </si>
+  <si>
+    <t>250118a</t>
   </si>
 </sst>
 </file>
@@ -352,18 +368,12 @@
       <charset val="161"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -380,14 +390,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -727,15 +734,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E13C670F-3750-4A6B-AD4A-B1253DBB373A}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="49.59765625" style="1" customWidth="1"/>
     <col min="2" max="2" width="45.3984375" style="1" customWidth="1"/>
     <col min="3" max="3" width="4.296875" style="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.69921875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="53.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
@@ -769,8 +776,10 @@
       <c r="C2" s="1">
         <v>5</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="2">
+        <v>250101</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -803,7 +812,9 @@
       <c r="C5" s="1">
         <v>6</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
@@ -815,7 +826,9 @@
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2">
+        <v>250105</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
@@ -824,8 +837,12 @@
       <c r="C7" s="1">
         <v>8</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="D7" s="2">
+        <v>250106</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
@@ -834,8 +851,12 @@
       <c r="C8" s="1">
         <v>4</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="D8" s="2">
+        <v>250107</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="243.6" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
@@ -957,15 +978,19 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="D18" s="2">
+        <v>250117</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="F18" s="1" t="s">
         <v>45</v>
       </c>
@@ -980,8 +1005,17 @@
       <c r="C19" s="1">
         <v>5</v>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
+      <c r="D19" s="2">
+        <v>250118</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793AADE0-1806-49EC-906F-A4BBAEE3F6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10D87EE6-A85F-4E89-A50E-2CE2B3A7C5CF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="25년 1회" sheetId="1" r:id="rId1"/>
+    <sheet name="25년 2회" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
   <si>
     <t>문제</t>
   </si>
@@ -331,6 +332,247 @@
   </si>
   <si>
     <t>250118a</t>
+  </si>
+  <si>
+    <t>3[Ω]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35.56[lx]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 감지선
+나) 정온식 스포트형 감지기
+다) 중계기
+라) 비상벨 또는 경보벨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 자동화재탐지설비의 평면도이다. 다음 조건을 참고하여 표의 산출식 및 총물량을 산출하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>천장의 높이는 4[m]이고 반자는 없으며 발신기세트와 수신기는 바닥으로부터 1.2[m]의 높이에 설치되어 있으며, 배선의 할증은 10[%]를 적용한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청각장애인용 시각경보장치의 설치기준을 3가지만 쓰시오.(단, 화재안전기술기준 각 호의 내용을 1가지로 본다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 복도ㆍ통로ㆍ청각장애인용 객실 및 공용으로 사용하는 거실에 설치하며, 각 부분에서 유효하게 경보를 발할 수 있는 위치에 설치할 것
+② 공연장ㆍ집회장ㆍ관람장 또는 이와 유사한 장소에 설치하는 경우에는 시선이 집중되는 무대부 부분 등에 설치할 것
+③ 바닥에서 2~2.5[m] 이하의 높이에 설치할 것(단, 천장높이가 2[m] 이하는 천장에서 0.15[m] 이내의 장소에 설치할 것)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>열반도체식 감지기의 부착높이 및 소방대상물의 구분에 따른 설치면적기준이다. 다음 표의 ①~⑥에 해당하는 면적을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 65[m²]
+② 36[m²]
+③ 40[m²]
+④ 23[m²]
+⑤ 30[m²]
+⑥ 23[m²]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P형 수신기와 감지기와의 배선회로에서 P형 수신기 종단저항은 20[kΩ], 감시전류는 1.17[mA], 릴레이 저항은 500[Ω], DC 24[V]일 경우 감지기가 동작할 때의 전류(동작전류)는 몇 [mA]인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상콘센트설비를 설치하여야 할 특정소방대상물 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 11층 이상의 층
+② 지하 3층 이상이고 지하층의 바닥면적 합계가 1000[m²] 이상인 것은 지하 전층
+③ 터널길이 500[m] 이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음에 주어진 진리표를 보고 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재안전기술기준에서 정하는 누전경보기의 용어 정의를 설명한 것이다. 다음 (  ) 안에 알맞은 용어를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 누전경보기
+② 수신부
+③ 변류기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ( ① )란 내화구조가 아닌 건축물로서 벽, 바닥 또는 천장의 전부나 일부를 불연재료 또는 준불연재료가 아닌 재료에 철망을 넣어 만든 건물의 전기설비로부터 누설전류를 탐지하여 경보를 발하며 변류기와 수신부로 구성된 것을 말한다.
+ㆍ ( ② )란 변류기로부터 검출된 신호를 수신하여 누전의 발생을 해당 특정소방대상물의 관계인에게 경보하여 주는 것(차단기구를 갖는 것을 포함)을 말한다.
+ㆍ( ③ )란 경계전로의 누설전류를 자동적으로 검출하여 이를 누전경보기의 수신부에 송신하는 것을 말한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연기감지기의 설치기준에 관해 다음 빈칸을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 배기구
+② 0.6[m]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ천장 또는 반자 부근에 ( ① )가 있는 경우에는 그 부근에 설치할 것
+ㆍ감지기는 벽 또는 보로부터 ( ② ) 이상 떨어진 곳에 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방시설공사업법령상 상주공사감리 대상기준에 관해 다음 빈칸을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 30000
+② 16
+③ 500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ연면적 ( ① )[m²] 이상의 특정소방대상물(아파트 제외)에 대한 소방시설의 공사
+ㆍ지하층을 포함한 층수가 ( ② )층 이상으로서 ( ③ )세대 이상인 아파트에 대한 소방시설의 공사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3선식 배선에 의하여 상시 충전되는 유도등의 전기회로에 점멸기를 설치하는 경우에는 어느 때에 점등되도록 하여야 하는지 그 기준을 5가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 자동화재탐지설비의 감지기 또는 발신기가 작동되는 때
+② 비상경보설비의 발신기가 작동되는 때
+③ 상용전원이 정전되거나 전원선이 단선되는 때
+④ 방재업무를 통제하는 곳 또는 전기실의 배전반에서 수동으로 점등하는 때
+⑤ 자동소화설비가 작동되는 때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 발신기에서 표시등 40[mA/1개], 경종 50[mA/1개]로 1회로당 90[mA]의 전류가 소모되며, 지상 6층의 각 층별 2회로씩 총 12회로인 공장에서 P형 수신반 최말단 발신기까지 500[m] 떨어진 경우 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 표시등 및 경종의 최대 소요전류와  총 소유전류를 구하시오.
+ - 표시등의 최대 소요전류
+ - 경종의 최대 소요전류
+ - 총 소요전류
+나) 사용전선의 종류
+다) 2.5[mm²]의 전선을 사용한 경우 최말단 경종 동작시 전압강하는 얼마인지 계산하시오.
+라) 다)의 계산에 의한 경종 작동 여부를 설명하시오.
+마) 전층 일제경보방식을 설치할 수 있는 특정소방대상물의 범위를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 
+ - 표시등의 최대 소요전류 : 40×12 = 480[mA] = 0.48[A]
+ - 경종의 최대 소요전류 : 50×12 = 600[mA] = 0.6[A]
+ - 총 소요전류 : 0.48+0.6 = 1.08[A]
+나) 450/750[V] 저독성 난연 가교폴리올레핀 절연전선
+다) e = (35.6×500×0.58) / (1000×2.5) = 4.129 = 4.13[V]
+라) Vr = 24-4.13 = 19.87[V] 로서 24×0.8 = 19.2[V] 이상이므로 정상 작동
+마) 11층(공동주택 16층) 미만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 중계기 설치기준 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 수신기와 감지기 사이에 설치(단, 수신기에서 도통시험을 하지 않을 때)
+② 조작 및 점검에 편리하고 화재 및 침수 등의 재해로 인한 피해를 받을 우려가 없는 장소에 설치
+③ 전원입력측에 과전류차단기 설치(수신기를 거쳐 전원공급이 안될 경우)하고 전원의 정전이 즉시 수신기에 표시되도록 할 것, 상용전원 및 예비전원의 시험을 할 수 있을 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어떤 건물의 사무실 바닥면적이 500[m²]이고, 천장높이가 3.5[m]로서 내화구조이다. 이 사무실에 차동식 스포트형(2종) 감지기를 설치하려고 한다. 최소 몇 개가 필요한지 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ500/70 = 7.1 = 8개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역률 82[%], 용량 500[kW] 유도전동기가 있다. 콘덴서의 용량이 200[kVA]일 때, 개선 후 역률 [%]을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주어진 동작설명이 적합하도록 미완성된 시퀀스 제어회로를 완성하시오. (단, 각 접점 및 스위치에는 접점명칭을 반드시 기입한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 전원을 투입하면 표시램프 GL이 점등된다.
+② 전동기 운전용 누름버튼스위치 PB-on을 누르면 전자접촉기 MC가 여자되어 전동기가 기동되며, 동시에 타이머 T가 통전되며 순시접점인 T-a접점에 의하여 전동기 운전표시등 RL이 점등된다. 이때 전자접촉기 b접점인 MC-b에 의하여 GL이 소등된다. 타이머 설정시간 후에 타이머의 한시b접점 T-b가 열리므로 전자접촉기 MC가 소자되어 전동기가 정지하고, 모든 접점은 PB-on을 누르기전의 상태로 복귀한다.
+③ 전동기가 정상운전 중이라도 정지용 누름버튼스위치 PB-off를 누르면 PB-on을 누르기 전의 상태로 된다.
+④ 전동기에 과전류가 흐르면 열동계전기 접점인 THR-a접점이 동작하여 전동기는 정지하고 모든 접점은 PB-on을 누르기 전의 상태로 복귀한다. 이때 경고등 YL이 점등된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 비상경보설비의 화재안전기술기준 중 발신기 설치기준에 대한 내용이다. 다음 빈칸에 알맞은 답을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ특정소방대상물의 ( ① )설치하되, 해당 층의 각 부분으로부터 하나의 발신기까지의 ( ② )가 25[m] 이하가 되도록 할 것
+ㆍ음량은 음향장치의 중심에서 ( ③ )떨어진 위치에서 ( ④ )이상일 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 층마다
+② 수평거리
+③ 1[m]
+④ 90[dB]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 유도등 및 유도표지의 화재안전성능기준 중 유도표지 설치기준에 대한 내용이다. 빈칸에 들어갈 알맞은 답을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 15[m]
+② 출입구 상단
+③ 통로유도표지
+④ 축광방식
+⑤ 비상조명등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ계단에 설치하는 것을 제외하고는 각 층마다 복도 및 통로의 각 부분으로부터 하나의 유도표지까지의 보행거리가 ( ① )이하가 되는 곳과 구부러진 모퉁이의 벽에 설치할 것
+ㆍ피난구유도표지는 ( ② )에 설치하되, ( ③ ) 는 바닥으로부터 높이 1[m] 이하의 위치에 설치할 것
+ㆍ( ④ )의 유도표지는 외광 또는 조명장치에 의하여 상시 조명이 제공되거나 ( ⑤ )에 의한 조명이 제공되도록 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수신기에서 45[m] 떨어진 장소에 단상 220[V], 1층과 2층에 아래 표와 같이 주어졌을 때 1층 및 2층의 전선의 최소 굵기를 구하시오. (단, 전압강하는 6[V] 이하로 하고, 각 층은 전선이 구분되어 있다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250201a, 250201a(1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250203a</t>
+  </si>
+  <si>
+    <t>250206a(2), 250206a(1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250206(1), 250206(2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250215a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250218a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -390,14 +632,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -734,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E13C670F-3750-4A6B-AD4A-B1253DBB373A}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="49.59765625" style="1" customWidth="1"/>
@@ -776,7 +1015,7 @@
       <c r="C2" s="1">
         <v>5</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>250101</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -802,17 +1041,20 @@
         <v>5</v>
       </c>
       <c r="D4" s="1">
-        <v>25103</v>
+        <v>250103</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="B5" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="C5" s="1">
         <v>6</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -823,10 +1065,13 @@
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="B6" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>250105</v>
       </c>
     </row>
@@ -837,24 +1082,27 @@
       <c r="C7" s="1">
         <v>8</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>250106</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="B8" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="C8" s="1">
         <v>4</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>250107</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -978,17 +1226,17 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="1">
         <v>250117</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -1005,16 +1253,288 @@
       <c r="C19" s="1">
         <v>5</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>250118</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B20" s="1">
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F4D140-F625-46C7-BF54-7660D0FA16E6}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="49.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="1">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1">
+        <v>250201</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="1">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="1">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1">
+        <v>250204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="1">
+        <v>6</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="1">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="1">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1">
+        <v>250214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1">
+        <v>250215</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="1">
+        <v>6</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5</v>
+      </c>
+      <c r="D19" s="1">
+        <v>250818</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10D87EE6-A85F-4E89-A50E-2CE2B3A7C5CF}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD56762B-186D-4135-A583-7AFEE5D3F5AF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="25년 1회" sheetId="1" r:id="rId1"/>
@@ -1531,7 +1531,7 @@
         <v>5</v>
       </c>
       <c r="D19" s="1">
-        <v>250818</v>
+        <v>250218</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>99</v>

--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD56762B-186D-4135-A583-7AFEE5D3F5AF}"/>
+  <xr:revisionPtr revIDLastSave="262" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8051485A-5EED-4EAD-8B89-41AD011D205A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="2" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="25년 1회" sheetId="1" r:id="rId1"/>
     <sheet name="25년 2회" sheetId="2" r:id="rId2"/>
+    <sheet name="25년 3회" sheetId="3" r:id="rId3"/>
+    <sheet name="24년 1회" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="189">
   <si>
     <t>문제</t>
   </si>
@@ -574,12 +576,622 @@
     <t>250218a</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>차동식 분포형 감지기의 종류 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 공기관식
+② 열전대식
+③ 열반도체식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥내소화전설비의 비상전원 및 상용전원에 대한 다음 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(가) 옥내소화전설비에 비상전원을 설치하여야 하는 경우이다. (   ) 안에 알맞은 내용을 쓰시오. 
+ - 층수가 7층으로서 연면적인 ( ① )[m²] 이상인 것
+ - 위에 해당하지 않는 경우로서 지하층의 바닥면적의 합계가 ( ② )[m²] 이상인 것
+(나) 다음은 옥내소화전설비 비상전원의 설치기준에 대한 사항이다. (  )안에 알맞은 내용을 쓰시오.
+ - 비상전원(내연기관의 기동 및 제어용 축전기 제외)의 설치장소는 다른 장소와 ( ③ )할 것. 이 경우 그 장소에는 비상전원의 공급에 필요한 기구나 설비 외의 것 (열병합발전설비에 필요한 기구나 설비 제외)을 두어서는 아니 된다.
+ - 비상전원을 실내에 설치하는 떄에는 그 실내에 ( ④ )을 설치할 것
+ - 상용전원이 저압수전인 경우에는 인입개폐기 직후에서 분기하여 ( ⑤ ) 배선으로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 2000
+② 3000
+③ 방화구획
+④ 비상조명
+⑤ 전용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제어벡효과의 정의를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서로 다른 두 금속을 접속하여 접속점에 온도차를 주면 열기전력이 발생하는 효과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비 미 시각경보장치의 화재안전기술기준에서 배선의 설치기준에 관한 다음 각 물음과 빈칸에 알맞은 답을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(가) P형 수신기 및 지피형 수신기의 감지기회로의 배선에 있어서 하나의 공통선에 접속할 수 있는 경계구역은 몇 개 이하로 하여야 하는가? 
+(나) 자동화재탐지설비의 감지기회로의 전로저항은 ( ① ) 이하가 되도록 해야 하며, 수신기의 각 회로별 종단에 설치되는 감지기에 접속되는 배선의 전압은 감지기 정격전압의 ( ② )이상이어야 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(가) 7개
+(나)
+ ① 50[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Ω</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]
+ ② 80[%]</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(가) 이온화식 감지기(스포트형)
+(나) 광전식 연기감지기(스포트형)
+(다) 통로유도등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림과 같은 복도에 자동화재탐지설비의 감지기를 설치하고자 한다. 각각의 도면에 연기감지기 2종과 연기감지기 3종을 배치하고 감지기 간 및 복도와 감지기 간 거리를 각각 기재하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단상교류 220[V]인 비상콘센트 플러그접속기의 칼받이의 접지극에 적용하는 접지시스템은 무엇이며 구리를 사용하는 접지도체의 최소 단면적은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ㆍ접지시스템 : 
+ㆍ최소단면적 : </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ접지시스템 : 보호 접지
+ㆍ최소단면적 : 6[mm²]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 그림을 보고 감지기의 종류를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 차동식 스포트형 감지기
+2. 보상식 스포트형 감지기
+3. 정온식 스포트형 감지기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림은 옥상에 시설된 탱크에 물을 올리는 데 사용되는 양수펌프의 수동 및 자동제어 운전회로도이다. 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조건]
+① 기계기구
+ - 운전용 누름버튼스위치(on, off) 각 1개
+ - 열동계전기(THR) 1개
+ - 전자접촉기 a접점 1개
+ - 전자접초기 b접점 1개
+② 운전조건
+ - 자동운전과 수동운전이 가능하도록 하여야 한다.
+ - 자동운전인 경우에는 다음과 같이 동작되도록 한다.
+   1. 저수위가 되면 FLS가 검출하여 전자접초긱가 여자되고 전동기가 운전된다.
+   2. 이때 RL 램프도 점등되고 GL램프는 소등된다.
+ - 수동운전인 경우에는 다음과 같이 동작되도록 한다.
+   1. 운전용 누름버튼스위치에 의하여 전자접촉기가 여자되어 전동기가 운전되도록 한다. 이때 RL램프가 점등되며 GL램프가 소등된다.
+   2. 전동기운전 중 과부하 또는 과열이 발생되면 열동계전기가 동작되어 전동기가 정지되도록 한다. (단, 자동운전시에서도 열동계전기가 동작하면 전동기가 정지하도록 한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>길이 30[m], 폭 20[m]인 방재센터가 있다. 여기에 조명률 60[%], 전광속도 2400[lm]의 40[W] 형광등이 몇 등 있어야 최소 150[lx] 이상의 조도를 얻을 수 있는 계산하시오. (단, 층고는 4[m]이며, 조명유지율은 80[%]이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">전기방식이 단상 2선식인 회로에서 고유저항 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>ρ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 전압강하 e, 선로길이 L, 부하전류 I, 전선의 단면적 A라고 할 때 전압강하의 유도식을 쓰시오.(단, 전선은 연동선을 사용한다.)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림과 같은 건물평면도의 경우 자동화재탐지설비의 최소 경계구역의 수를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일시적으로 발생된 열, 연기 또는 먼지 등으로 연기감지기가 화재신호를 발신할 우려가 있는 곳에 축적기능 등이 있는 자동화재탐지설비의 수신기를 설치하여야 한다. 이 경우에 해당하는 장소 3가지를 쓰시오. (단, 축적형 감지기가 설치되지 아니한 장소이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 지하층ㆍ무창층 등으로서 환기가 잘 되지 아니하는 장소
+② 지하층ㆍ무창층 등으로서 실내면적이 40[m²] 미만인 장소
+③ 감지기의 부착면과 실내 바닥과의 거리가 2.3[m] 이하인 장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 화재안전기술기준에서 정한 연기감지기의 설치기준이다. 다음 (  ) 안의 ① ~ ⑧에 알맞은 답을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">① 150
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">② 50
+③ 20
+④ 30
+⑤ 20
+⑥ 15
+⑦ 10
+⑧ 0.6
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하자보수대상 소방시설 중 하자보수 보증기간이 2년인 소방시설 6가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 유도등
+② 피난기구
+③ 비상조명등
+④ 비상경보설비
+⑤ 비상방송설비
+⑥ 무선통신보조설비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>습식 스프링클러설비의 작동순서로 다음 (  )안에 알맞은 답을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 헤드개방
+② 유수검지(압력스위치 작동)
+③ 소화설비반에 신호(수시반)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회로의 논리식 Y에 대한 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 옥내소화전설비 감시제어반의 기능에 대한 적합기준이다. (  )안을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 표시등
+② 음향경보
+③ 저수위
+④ 도통
+⑤ 작동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ각 펌프의 작동여부를 확인할 수 있는 ( ① ) 및 ( ② ) 기능이 있어야 할 것
+ㆍ수조 또는 물올림수조가 ( ③ )로 될 때 표시등 및 음향으로 경보할 것
+ㆍ각 확인회로(기동용 수압개폐장치의 압력스위치회로ㆍ수조 또는 물올림수조의 저수위감시회로ㆍ급수배관에 설치되어 있는 개폐밸브의 폐쇄상태 확인회로를 말한다.)마다 ( ④ )시험 및 ( ⑤ ) 시험을 할 수 있어야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연축전지와 알칼리축전지에 대한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 그림은 연축전지에 대한 반응식이다. 빈칸에 들어갈 알맞은 것을 적으시오.
+나) 연축전지와 알칼리축전지의 공칭전압은 각각 몇 [V/cell]인지 쓰시오.
+ - 연축전지 :
+ - 알칼리축전지 : 
+다) 그림과 같은 충전방식을 쓰시오.
+라) 200[V]의 비상용 조명부하를 60[W] 100등, 30[W] 70등을 설치하려고 한다. 연축전지 HS형 110[cell], 시간은 30분, 최저축전지온도는 5[℃], 최저허용전압은 195[V]일 때 점등에 필요한 축전지의 용량 [Ah]을 구하시오.(단, 보수율은 0.8, 용량환산시간계수는 1.2이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가로 20[m], 세로 15[m]인 방재센터에 동일한 비상조명등이 40개 설치되어 있다. 비상조명등이 모두 점등되었을 때 광속[lm]을 구하시오. (단, 비상조명등 1개의 조도는 100[lx], 조명률 50[%], 유지율은 85[%]이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부착높이 15[m] 이상 20[m] 미만에 설치가능한 감지기 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 이온화식 1종
+② 광전식(스포트형, 분리형, 공기흡입형) 1종
+③ 연기복합형
+④ 불꽃감지기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지상 10[m]되는 곳에 1000[m³]의 저수조가 있다. 이 저수조에 양수하기 위하여 펌프효율이 80[%], 여유계수가 1.2, 용량이 15[kW]인 전동기를 사용한다면 몇 분 후에 저수조에 물이 가득 차겠는지 구하시오. (단, 답안 작성시 소수점은 버릴 것)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 비상콘센트설비의 화재안전성능기준에 대한 내용이다. 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>가) 하나의 전용회로에 설치하는 비상콘센트는 7개이다. 이 경우 전선의 용량은 비상콘센트 몇 개의 공급용량을 합한 용량 이상의 것으로 하여야 하는가?
+나) 비상콘센트의 보호함 상부에 설치하는 표시등의 색은 무슨 색인가?
+다) 비상콘센트설비의 전원부와 외함 사이를 500[V] 절연저항계로 측정할 때 30[M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Ω</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]으로 측정되었다. 절연저항의 적합여부와 그 이유를 쓰시오.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>가) 3개
+나) 적색
+다) 
+ - 적합여부 : 적합
+ - 이유 : 20[M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Ω</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>] 이상이므로</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비 및 시각경보장치의 화재안전기준 중 감지기회로의 도통시험을 위한 종단저항 설치기준 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 점검 및 관리가 쉬운 장소에 설치
+② 바닥에서 1.5m 이내의 높이에 설치(전용함 설치시)
+③ 감지기회로의 끝부분에 설치하며, 종단감지기에 설치할 경우에는 구별이 쉽도록 해당 감지기의 기판 및 감기지 외부 등에 별도의 표시를 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림과 같은 시퀀스회로에서 푸시버튼스위치 PB를 누르고 있을 때 타이머 T₁(설정시간 : t₁), T₂(설정시간 : t₂), 릴레이 X₁, X₂, 표시등 PL에 대한 타임차트를 완성하시오. (단, T₁은 1초 T₂는 2초이며 설정시간 이외의 시간지연은 없다고 본다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 누전경보기의 화재안전기술기준 중 설치방법에 대한 내용이다. 다음 빈칸에 알맞은 답을 적으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 경계전로의 정격전류가 ( ① )를 초과하는 전로에 있어서는 1급 누전경보기를, ( ① )이하의 전로에 있어서는 ( ② ) 누전경보기 또는 ( ③ ) 누전경보기를 설치할 것. 다만, 정격전류가 ( ① )를 초과하는 경계전로가 분기되어 각 분기회로의 정격전류가 ( ① ) 이하가 되는 경우 해당 분기회로마다 ( ③ ) 누전경보기를 설치할 때에는 해당 경계전로에 ( ② ) 누전경보기를 설치한 것으로 본다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 60[A]
+② 1급
+③ 2급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상콘센트설비의 화재안전기술기준에 관한 내용이다. 빈칸에 알맞은 내용을 적으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ비상콘센트설비의 전원회로는 단상교류 ( ① )인 것으로서, 그 공급용량은 1.5[kVA] 이상인 것으로 할 것
+ㆍ비상콘센트의 플러그접속기는 ( ② ) 플러그접속기 (KS C 8305)를 사용해야 한다.
+ㆍ비상콘센트의 플러그접속기의 ( ③ )에는 접지공사를 해야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 220[V]
+② 접지형 2극
+③ 칼받이 접지극</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 단독경보형감지기의 화재안전성능기준 중 설치기준에 관련된 내용이다. 빈칸에 알맞은 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ각 실마다 설치하되, 바닥면적 ( ① )[m²]를 초과하는 경우에는 ( ① )[m²] 마다 ( ② )이상 설치하여야 한다.
+ㆍ최상층의 ( ③ )의 천장에 설치할 것
+ㆍ ( ④ )를 주전원으로 사용하는 단독경보형감지기는 정상적인 작동상태를 유지할 수 있도록 주기적으로 건전지를 교환할 것
+ㆍ상용전원을 주전원으로 사용하는 단독경보형감지기의 ( ⑤ )는 제품검사에 합격한 것을 사용 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 150
+② 1개
+③ 계단실
+④ 건전지
+⑤ 2차 전지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음의 표와 같이 두 입력 A와 B가 주어질 때 주어진 논리소자의 명칭과 출력에 대한 진리표를 완성하시오. (단, ①~⑦은 각각 세로가 모두 맞아야 정답으로 채점된다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3로스위치 2개를 설치하였을 경우 조건을 참고하여 점등, 소등이 되도록 다음 미완성 배선도를 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정소방대상물에 자동화재탐지설비용 공기관식 차동식 분포형 감지기를 설치하고자 한다. 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 일반구조인 경우와 내화구조인 경우의 공기관 상호간의 거리는 각각 몇 [m] 이하이어야하는가?
+ - 일반구조 :
+ - 내화구조 : 
+나) 하나의 검출 부분에 접속하는 공기관의 길이는 몇 [m] 이하이어야 하는가?
+다) 바닥으로부터의 높이 조건을 상세히 적으시오.
+라) 감지구역마다 공기관의 노출 부분의 길이는 몇 [m] 이상이어야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 
+ - 일반구조 : 6[m]
+ - 내화구조 : 9[m]
+나) 100[m]
+다) 바닥으로부터 0.8[m] 이상 1.5[m] 이하의 위치에 설치
+라) 20[m]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누전경보기의 화재안전기술 중 전원에 대한 기준 3가지를 적으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 분전반으로부터 전용회로로 하고, 각 극에 개폐기 및 15[A] 이하의 과전류차단기(배선용 차단기는 20[A] 이하의 것으로 각 극을 개폐할 수 있는 것) 설치
+② 분기할 때는 다른 차단기에 따라 전원이 차단되지 않도록 할 것
+③ 개폐기에는 "누전경보기용"이라고 표시한 표지를 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상방송을 할 때에는 자동화재탐지설비의 지구음향장치의 작동을 정지시킬 수 있는 미완성 결선도를 다음 범례를 이용하여 조건에 따라 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[범례] 및 [그림] 이미지 참고
+[조건] 
+① PB_on스위치 또는 LS가 동작하면 계전기 X₁이 여자되어 자기유지된다.
+② 계전기 X₁이 여자됨에 따라 지구경종이 작동한다.
+③ 자동절환스위치가 비상방송설비로 절환되면 릴레이 X₂가 여자되어 지구경종이 정지된다. 평상시에는 자동절환위치가 자동화재탐지설비에 연결되어 있다.
+④ PB_off스위치가 동작하면 릴레이 X₁이 소자된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재에 의한 열, 연기 또는 불꽃(화염) 이외의 요인에 의하여 자동화재탐지설비가 작동하여 화재경보를 발하는 것을 "비화재보(Unwanted Alarm)"라 한다. 즉 자동화재탐지설비가 정상적으로 작동하였다고 하더라도 화재가 아닌 경우의 경보를 "비화재보"라 하며 비화재보의 종류는 다음과 같이 구분할 수 있다. [보기] 설명 중 일과성 비화재보로 볼 수 있는 Nuisance Alarm에 대한 방지책을 4가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 주위상황이 대부분 순간적으로 화재와 같은 상태(실제 화재와 유사한 환경이나 상황)로 되었다가 정상상태로 복귀하는 경우(일과서 비화재보 : Nuisance Alarm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 비화재보에 적응성이 있는 감지기 사용
+② 환경적응성이 있는 감지기 사용
+③ 감지기 설치수의 최소화
+④ 연기감지기의 설치 제한
+⑤ 경년변화에 따른 유지보수
+⑥ 아날로그 감지기와 인텔리전트 수신기의 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지하 3층, 지상 11층인 어느 특정소방대상물에 설치된 자동화재탐지설비의 음향장치의 설치기준에 관한 사항이다. 다음 표와 같이 화재가 발생하였을 경우 우선적으로 경보하여야 하는 층을 빈칸에 표시하시오. (단, 공동주택이 아니며, 경보표시는 ●를 사용한다. 각각 세로부분이 모두 맞아야 정답으로 채점된다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Φ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 380[V], 60[Hz], 4P, 50[HP]의 전동기가 있다 다음 각 물음에 답하시오.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 동기속도[rpm]를 구하시오.
+나) 회전수가 1730[rpm]일 때 슬립[%]을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250314a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(가) 부착높이에 따른 기준(표참고)
+(나) 감지기는 복도 및 통로에 있어서는 보행거리 ( ④ )[m] (3종에 있어서는 ( ⑤ )[m]마다, 계단 및 경사로에 있어서는 수직거리 ( ⑥ )[m] (3종에 있어서 ( ⑦ )[m])마다 1개 이상으로 할 것
+(다) 감지기는 벽 또는 보로부터 ( ⑧ )[m] 이상 떨어진 곳에 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250316a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 이 회로의 유접점회로를 그리시오.
+(나) 논리식을 NAND회로만 사용하여 무접점회로를 그리시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250317a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가) PbSO₄
+나) 
+ - 연축전지 : 2[V/cell]
+ - 알칼리축전지 : 1.2[V/cell]
+다) 부동충전방식
+라) 축전지 용량 : 60.75[Ah]
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250317(1, 250317(2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250306a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250305a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250308a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250309a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250312a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가)
+ - (10×40)/600 ≒ 1
+ - (10×50)/600 ≒ 1 
+ - 총 : 2
+나) 
+ - (10×40)/600 ≒ 1
+ - (10×50)/600 ≒ 1
+ - (10×50)/600 ≒ 1
+ - 총 : 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240117a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240101a(1,
+240101a(2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240107a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240109a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240112a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240115a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -609,13 +1221,34 @@
       <family val="2"/>
       <charset val="161"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -632,11 +1265,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -654,6 +1296,130 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>188258</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>909917</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6A5C435-F807-958F-8744-56E83800845F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7879976" y="16391964"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>188258</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>224117</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1B538A8-997C-4EC8-B4CE-1335F363BD36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7879976" y="3146611"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1541,4 +2307,624 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32C738B9-DB35-4A96-9B8F-B28B29EC88A3}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="49.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="278.39999999999998" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="1">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="1">
+        <v>6</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="4">
+        <v>6</v>
+      </c>
+      <c r="D6" s="4">
+        <v>250305</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="4">
+        <v>6</v>
+      </c>
+      <c r="D7" s="4">
+        <v>250306</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="1">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="330.6" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="1">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4">
+        <v>250309</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="4">
+        <v>250310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4">
+        <v>250311</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C13" s="1">
+        <v>6</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="1">
+        <v>8</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="1">
+        <v>6</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8356F92-3276-4DC6-8CDE-4BB37304F424}">
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="49.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="1">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4">
+        <v>240101</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4">
+        <v>240102</v>
+      </c>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4">
+        <v>240104</v>
+      </c>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="1">
+        <v>6</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="1">
+        <v>6</v>
+      </c>
+      <c r="D8" s="4">
+        <v>240107</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="1">
+        <v>6</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="1">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4">
+        <v>240109</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D13" s="4">
+        <v>240112</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="1">
+        <v>8</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="1">
+        <v>5</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="4">
+        <v>240115</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C17" s="1">
+        <v>8</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="D18" s="4">
+        <v>240117</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="262" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8051485A-5EED-4EAD-8B89-41AD011D205A}"/>
+  <xr:revisionPtr revIDLastSave="272" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{952BEFA0-8061-49EA-AAEB-A34A6589BFB1}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="2" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="25년 1회" sheetId="1" r:id="rId1"/>
     <sheet name="25년 2회" sheetId="2" r:id="rId2"/>
     <sheet name="25년 3회" sheetId="3" r:id="rId3"/>
     <sheet name="24년 1회" sheetId="5" r:id="rId4"/>
+    <sheet name="24년 2회" sheetId="6" r:id="rId5"/>
+    <sheet name="24년 3회" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="189">
   <si>
     <t>문제</t>
   </si>
@@ -1265,7 +1267,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1275,10 +1277,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1382,6 +1381,126 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7879976" y="3146611"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>188258</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>224117</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4458D4A4-A047-48C5-ADB3-9562E722BF49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7876838" y="16805237"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>188258</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>224117</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56D0F10C-57BC-4AAD-B22D-5E458B4D44B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7876838" y="16805237"/>
           <a:ext cx="65" cy="172227"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2400,13 +2519,13 @@
       <c r="B6" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="1">
         <v>6</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="1">
         <v>250305</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="1" t="s">
         <v>178</v>
       </c>
     </row>
@@ -2414,13 +2533,13 @@
       <c r="A7" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="1">
         <v>250306</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="1" t="s">
         <v>177</v>
       </c>
     </row>
@@ -2448,7 +2567,7 @@
       <c r="C9" s="1">
         <v>6</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="1" t="s">
         <v>179</v>
       </c>
     </row>
@@ -2459,10 +2578,10 @@
       <c r="C10" s="1">
         <v>7</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="1">
         <v>250309</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="1" t="s">
         <v>180</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -2476,7 +2595,7 @@
       <c r="C11" s="1">
         <v>5</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="1">
         <v>250310</v>
       </c>
     </row>
@@ -2487,7 +2606,7 @@
       <c r="C12" s="1">
         <v>5</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="1">
         <v>250311</v>
       </c>
     </row>
@@ -2501,8 +2620,7 @@
       <c r="C13" s="1">
         <v>6</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="1" t="s">
         <v>181</v>
       </c>
     </row>
@@ -2528,7 +2646,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -2556,7 +2674,7 @@
       <c r="C17" s="1">
         <v>6</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="1" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2567,10 +2685,10 @@
       <c r="C18" s="1">
         <v>5</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="1" t="s">
         <v>174</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -2600,7 +2718,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8356F92-3276-4DC6-8CDE-4BB37304F424}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="49.59765625" style="1" customWidth="1"/>
@@ -2622,10 +2740,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -2642,10 +2760,10 @@
       <c r="C2" s="1">
         <v>8</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="1">
         <v>240101</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>184</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -2659,10 +2777,9 @@
       <c r="C3" s="1">
         <v>4</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="1">
         <v>240102</v>
       </c>
-      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
@@ -2674,8 +2791,6 @@
       <c r="C4" s="1">
         <v>4</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
@@ -2684,10 +2799,9 @@
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="1">
         <v>240104</v>
       </c>
-      <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
@@ -2699,8 +2813,6 @@
       <c r="C6" s="1">
         <v>6</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
       <c r="F6" s="1" t="s">
         <v>141</v>
       </c>
@@ -2715,8 +2827,6 @@
       <c r="C7" s="1">
         <v>4</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
@@ -2725,10 +2835,10 @@
       <c r="C8" s="1">
         <v>6</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="1">
         <v>240107</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="1" t="s">
         <v>185</v>
       </c>
     </row>
@@ -2742,8 +2852,6 @@
       <c r="C9" s="1">
         <v>6</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
       <c r="F9" s="1" t="s">
         <v>147</v>
       </c>
@@ -2755,10 +2863,10 @@
       <c r="C10" s="1">
         <v>7</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="1">
         <v>240109</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="1" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2772,8 +2880,6 @@
       <c r="C11" s="1">
         <v>3</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
       <c r="F11" s="1" t="s">
         <v>150</v>
       </c>
@@ -2788,8 +2894,6 @@
       <c r="C12" s="1">
         <v>5</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
       <c r="F12" s="1" t="s">
         <v>153</v>
       </c>
@@ -2798,10 +2902,10 @@
       <c r="A13" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="1">
         <v>240112</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="1" t="s">
         <v>187</v>
       </c>
     </row>
@@ -2815,8 +2919,6 @@
       <c r="C14" s="1">
         <v>8</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
       <c r="F14" s="1" t="s">
         <v>158</v>
       </c>
@@ -2831,8 +2933,6 @@
       <c r="C15" s="1">
         <v>5</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
@@ -2841,10 +2941,10 @@
       <c r="C16" s="1">
         <v>5</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="1">
         <v>240115</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="1" t="s">
         <v>188</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -2861,8 +2961,6 @@
       <c r="C17" s="1">
         <v>8</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
       <c r="F17" s="1" t="s">
         <v>165</v>
       </c>
@@ -2874,10 +2972,10 @@
       <c r="C18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="1">
         <v>240117</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="1" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2889,38 +2987,97 @@
         <v>5</v>
       </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="4"/>
       <c r="F19" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4448957A-E173-4547-AF9F-BC74A16A2E88}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="49.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D19" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594DE2EA-328C-4851-BB57-E5A31C071F26}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="49.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D19" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="272" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{952BEFA0-8061-49EA-AAEB-A34A6589BFB1}"/>
+  <xr:revisionPtr revIDLastSave="273" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DF30DC7-6987-47A2-9EDC-7058BA3B6FDA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="25년 1회" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="190">
   <si>
     <t>문제</t>
   </si>
@@ -1186,6 +1186,10 @@
   </si>
   <si>
     <t>240115a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250214, 250214(1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2359,8 +2363,8 @@
       <c r="C15" s="1">
         <v>5</v>
       </c>
-      <c r="D15" s="1">
-        <v>250214</v>
+      <c r="D15" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">

--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="273" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DF30DC7-6987-47A2-9EDC-7058BA3B6FDA}"/>
+  <xr:revisionPtr revIDLastSave="405" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B52A4CB-B459-4F0B-BC63-BF985F57318C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="25년 1회" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="25년 3회" sheetId="3" r:id="rId3"/>
     <sheet name="24년 1회" sheetId="5" r:id="rId4"/>
     <sheet name="24년 2회" sheetId="6" r:id="rId5"/>
-    <sheet name="24년 3회" sheetId="7" r:id="rId6"/>
+    <sheet name="24년 3회(작성중)" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="254">
   <si>
     <t>문제</t>
   </si>
@@ -1190,6 +1190,411 @@
   </si>
   <si>
     <t>250214, 250214(1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비 및 시각경보장치의 화재안전기준에서 배선의 설치기준에 관한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 감지기회로 및 부속회로의 전로와 대지 사이 및 배선 상호간의 절연저항은 1경계구역마다 직류 250[V}의 절연저항측정기를 사용하여 측정한 절연저항이 몇 [㏁] 이상이 되도록 하여야 하는가?
+나) 피(P형) 수신기 및 지퍼(G.P.)형 수신기의 감지기회로의 배선에 있어서 하나의 공통선에 접속할 수 있는 경계구역은 몇 개 이하로 하여야 하는가?
+다) 감지기회로의 도통시험을 위한 종단저항 설치기준 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 0.1[㏁]
+나) 7개
+다) 
+ - 점검 및 관리가 쉬운 장소에 설치할 것
+ - 전용함을 설치하는 경우 그 설치높이는 바닥으로부터 1.5[m] 이내로 할 것
+ - 감지기회로의 끝 부분에 설치하며, 종단감지기에 설치할 경우에는 구별이 쉽도록 해당 감지기의 기판 및 감지기 외부 등에 별도의 표시를 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥내소화전설비의 비상전원으로 자가발전설비 또는 축전지설비를 설치할 때 비상전원 설치기준 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 점검에 편리하고 화재 및 침수 등의 재해로 인한 피해를 받을 우려가 없는 곳에 설치
+② 옥내소화전설비를 유효하게 20분 이상 작동할 수 있을 것
+③ 상용전원으로부터 전력의 공급이 중단된 때에는 자동으로 비상전원으로부터 전력을 공급받을 수 있을 것
+④ 비상전원의 설치장소는 다른 장소와 방화구획하여야 하며, 그 장소에는 비상전원의 공급에 필요한 기구나 설비외의 것을 두지 말 것(단, 열병합 발전설비에 필요한 기구나 설비 제외)
+⑤ 비상전원을 실내에 설치하는 때에는 그 실내에 비상조명등 설치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 어느 특정소방대상물의 평면도이다. 건축물의 주요구조부는 내화구조이고, 층의 높이는 4.5[m]일 때 다음 각 물음에 답하시오.(단, 차동식 스포트형 감지기 1종을 설치한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240203a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공기관식 차동식 분포형 감지기의 설치도면이다. 다음 각 물음에 답하시오. (단, 주요구조부를 내화구조로 한 소방대상물인 경우이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가) 내화구조일 경우의 공기관 상호간의 거리와 감지구역의 각 변과의 거리는 몇 [m] 이하가 되도록 하여야 하는지 도면의 (  )안을 쓰시오.
+나) 공기관의 노출부분의 길이는 몇 [m] 이상이 되어야 하는지 쓰시오.
+다) 종단저항을 발신기에 설치할 경우 차동식 분포형 감지기의 검출기와 발신기 간에 연결해야 하는 전선의 가닥수를 도면에 표기하시오.
+라) 검출부의 설치높이를 쓰시오.
+마) 검출부분에 접속하는 공기관의 길이는 몇 m 이하로 하여야 하는지 쓰시오.
+바) 공기관의 재질을 쓰시오.
+사) 검출부의 경사도는 몇 도 미만이어야 하는지 쓰시오.
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240204a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 그림 참고
+나) 20[m]
+다) 바닥에서 0.8 ~ 1.5[m]
+마) 100[m]
+바) 중공동관(동관)
+사) 5도 (차동식 분포형 감지기는 = 5도 / 스포트형 감지기 = 45도)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지상 25[m]되는 곳에 수조가 있다. 이 수조에 분당 20[m³]의 물을 양수하는 펌프용 전동기를 설치하여 3상 전력을 공급하려고 한다. 단상 변압기 그대로 V결선하여 이용하고자 한다. 펌프 효율이 70[%]이고, 펌프측 동력에 15[%]의 여유를 둔다고 할 때 다음 각 물음에 답하시오. (단, 펌프용 3상 농형 유도전동기의 역률은 85[%]로 가정한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 펌프용 전동기의 용량은 몇 [kW]인가?
+나) 3상 전력을 공급하고자 단상 변압기 2대를 V결선하여 이용하고자 한다. 단상 변압기 1대의 용량은 몇 [kVA]인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 한국전기설비규정(KEC)에서 규정하는 전기적 접속에 대한 내용이다. (  ) 안에 알맞은 말을 넣으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 배선설비가 바닥, 벽, 지붕, 천장, 칸막이, 중공벽 등 건축구조물을 관통하는 경우, 배선설비가 통과한 후에 남는 개구부는 관통 전의 건축구조 각 부재에 규정된 ( ① )에 따라 밀폐하여야 한다.
+나) 내화성능이 규정된 건축구조부재를 관통하는 ( ② )는 제 1에서 요구한 외부의 밀폐와 마찬가지로 관통 전에 각 부의 내화등급이 되도록 내부도 밀폐하여야 한다.
+다) 관련 제품 표준에서 자기소화성으로 분류되고 최대 내부단면적이 ( ③ )[mm²] 이하인 전선관, 케이블트렁킹 및 ( ④ )은 다음과 같은 경우라면 내부적으로 밀폐하지 않아도 된다.
+ ㆍ보호등급 IP33에 관한 KS C IEC 60529(외곽의 방진보호 및 방수보호등급)의 시험에 합격한 경우
+ ㆍ관통하는 건축 구조체에 의해 분리된 구획의 하나 안에 있는 배선설비의 단말이 보호등급 IP33에 관한 KS C IEC 60529[외함의 밀폐 보호등급 구분(IP코드)]의 시험에 합격한 경우
+라) 배선설비는 그 용도가 ( ⑤ ) 을 견디는데 사용되는 건축구조부재를 관통해서는 안 된다. 다만, 관통 후에도 그 부재가 하중에 견딘다는 것을 보증할 수 있는 경우는 제외한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 내화등급
+② 배선설비
+③ 710
+④ 케이블덕팅시스템
+⑤ 하중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>차동식 스포트형 감지기의 구조에 관한 다음 그림에서 주어진 번호의 명칭을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240207a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 고정접점
+② 리크콩 = 리크구멍
+③ 다이어프램
+④ 감열실 = 공기실
+⑤ 배선
+⑥ 가동접점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이산화탄소 소화설비의 음향경보장치를 설치하려고 한다. 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 방호구역 또는 방호대상물이 있는 구획의 각 부분으로부터 하나의 확성기까지의 수평거리는 몇 [m] 이하로 하여야 하는가?
+나) 소화약제의 방출 개시 후 몇 분 이상 경보를 발하여야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 25[m]
+나) 1분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가스누설경보기를 설치하여야 하는 대상을 5가지 쓰시오.(단, 가스시설이 설치된 경우만 해당한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">① 문화 및 집회시설
+② 종교시설
+③ 판매시설
+④ 운수시설
+⑤ 의료시설
+⑥ 노유자시설
+⑦ 수련시설
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>⑧ 운동시설
+⑨ 숙박시설
+⑩ 물류터미널
+⑪ 장례시설</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 비상콘센트 보호함의 시설기준이다. (  )안에 알맞은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ보호함에는 쉽게 개폐할 수 있는 ( ① )을 설치하여야 한다.
+ㆍ비상콘센트의 보호함 표면에 ( ② )라고 표시한 표지를 하여야 한다.
+ㆍ비상콘센트의 보호함 상부에 ( ③ )의 ( ④ )을 설치하여야 한다. 다만, 비상콘센트의 보호함을 옥내 소화전함 등과 접속하여 설치하는 경우에는 ( ⑤ )등의 표시등과 겸용할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 문
+② 비상콘센트
+③ 적색
+④ 표시등
+⑤ 옥내소화전함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 화재안전기준에 따른 내화배선의 공사방법에 관한 사항이다. (  )안에 알맞은 말을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 금속관ㆍ2종 금속제 가요전선관 또는 ( ① )에 수납하여 내화구조로 된 벽 또는 바닥 등에 벽 또는 바닥의 표면으로부터 ( ② )[mm] 이상의 깊이로 매설하여야 한다. 다만, 다음의 기준에 적합하게 설치하는 경우에는 그러하지 아니하다.
+ - 배선을 내화성능을 갖는 배선전용실 또는 배선용 샤프트ㆍ피트ㆍ덕트 등에 설치하는 경우
+ - 배선전용실 또는 배선용 샤프트ㆍ피트ㆍ덕트 등에 다른 설비의 배선이 있는 경우에는 이로부터 ( ③ )[cm] 이상 떨어지게 하거나 소화설비의 배선과 이웃하는 다른 설비의 배선 사이에 배선지름(배선의 지름이 다른 경우에는 가장 큰 것을 기준으로 한다.)의 ( ④ ) 배 이상의 높이의 불연성 격벽을 설치하는 경우
+나) 내화전선은 ( ⑤ ) 공사의 방법에 따라 설치해야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 합성수지관
+② 25
+③ 15
+④ 1.5
+⑤ 케이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공사비 산출내역서 작성시 표준품셈표에서 정하는 공구손료의 적용범위를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>직접노무비의 3[%] 이내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상콘센트설비의 사용전원회로의 배선은 다음의 경우에 어디에서 분기하여 전용배선으로 하는지를 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 저압수전인 경우 : 
+나) 특고압수전 또는 고압수전인 경우 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 저압수전인 경우 : 인입개폐기 직후에서
+나) 특고압수전 또는 고압수전인 경우 : 전력용 변압기 2차측의 주차단기 1차측 또는 2차측에서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>열전대식 차동식 분포형 감지기는 제어백효과를 이용한 감지기이다. 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 제어백효과를 설명하시오.
+나) 열전대의 정의를 쓰시오.
+다) 열전대의 재료로 가장 우수한 금속은 무엇인지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가) 서로 다른 두 금속을 접속하여 접속점에 온도차를 주면 열기전력 발생하는 효과
+나) 서로 다른 종류의 금속을 접속하여 온도차에 의해 열기전력 발생
+다) 백금
+* 추가 설명
+ - 펠티에 효과 : 두 종류의 금속으로 된 회로에 전류를 흘리면 각 접속점에서 열의 흡수 또는 발생이 일어나는 현상
+ - 톰슨효과 : 균질의 철사에 온도구배가 있을 때 여기에 전류가 흐르면 열의 흡수 또는 발생이 일어나는 현상
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 누전경보기의 형식승인 및 제품검사의 기술기준에 대한 내용이다. 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가) 주위의 밝기가 몇 [lx]인 장소에서 측정하여야 앞면으로부터 3[m] 떨어진 곳에서 켜진 등이 확실히 식별되는가?
+나) 전구는 몇 개 이상을 병렬로 접속하여야 하는가?
+다) 누전경보기의 공칭작동전류치는 몇 [mA] 이하이어야 하는가?
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 300[lx]
+나) 2개 이상
+다) 200[mA] 이하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림과 같은 논리회로를 보고 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 논리식으로 표현하시오.
+나) AND, OR, NOT 회로를 이용한 등가회로로 그리시오.
+다) 유접점(릴레이)회로로 그리시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240216a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 발신기에서 표시등 = 30[mA/1개], 경종=50[mA/1개]로 1회당 80[mA]의 전류가 소모되며, 지하 1층, 지상 5층의 각 층별 2회로씩 총 12회로인 공장에서 P형 수신반 최말단 발신기까지 600[m] 떨어진 경우 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 표시등 및 경종의 최대소요전류와 총 소요전류를 구하시오.
+ - 표시등의 최대소요전류 : 
+ - 경종의 최대소요전류 : 
+ - 총 소요전류 : 
+나) 2.5[mm²]의 전선을 사용한 경우 최말단 경종 동작시 전압강하는 얼마인지 계산하시오.
+다) 자동화재타지설비의 음향장치는 정격전압의 몇 [%] 전압에서 음향을 발할 수 있어야 하는가?
+라) 나)의 계산에 의한 경종 작동여부를 설명하시오.
+ - 이유 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 표시등 및 경종의 최대소요전류와 총 소요전류를 구하시오.
+ - 표시등의 최대소요전류 : 30×12=360[mA] = 0.36[A] 
+ - 경종의 최대소요전류 : 50×12=600[mA] = 0.6[A}
+ - 총 소요전류 : 0.36+0.6=0.96[A]
+나) e = (35.6×600×0.46)/(1000×2.5)=3.93[V]
+다) 80[%]
+라) Vr=24-3.93 =20.07[V] 로서 24×0.8=19.2[V] 이상이므로 정상 작동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P형 수신기와 감지기와의 배선회로에서 종단저항은 4.7[㏀], 배선저항은 28[Ω], 릴레이저항은 12[Ω]이며, 회로전압이 DC 24[V]일 때 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 평소 감시전류는 몇 [mA]인가?
+나) 감지기가 동작할 때(화재시)의 전류는 몇 [mA]인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주어진 도면은 유도전동기 기동ㆍ정지회로의 미완성 도면이다. 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240301a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[동작설명] 
+① 전원을 투입하면 표시램프 GL이 점등되도록 한다.
+② 전동기 기동용 푸시버튼스위치를 누르면 전자접촉기 MC가 여자되고, MC-a접점에 의해 자기유지되며 RL이 점등된다. 동시에 전동기가 기동되고, GL등이 소등된다.
+③ 전동기가 정상운전 중 정지용 푸시버튼스위치를 누르거나 열동계전기가 작동되면 전동기는 정지하고 최초의 상태로 복귀한다.
+가) 주어진 보기의 접점을 이용하여 미완성된 보조회로(제어회로)를 완성하시오.
+나) 주회로에 대한 점선의 내부를 주어진 도면에 완성하시오.
+다) 열동계전기(THR)는 어떤 경우에 작동하는지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가), 나) 해설 참조
+다) 전동기에 과부하가 걸릴 때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누전경보기의 형식승인 및 제품검사의 기술기준을 참고하여 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 감도조정장치를 갖는 누전경보기의 최대치는 몇 [A] 이하인가?
+나) 다음 변류기의 전로개폐시험에 대한 내용이다. 빈칸을 완성하시오.
+ - 변류기는 출력단자에 부하저항을 접속하고, 경계전로에 해당 변류기의 정격전류의 150[%]인 전류를 흘린 상태에서 경계전로의 개폐를 (  )회 반복하는 경우 그 출력전압치는 공칭작동전류치의 42[%]에 대응하는 출력전아비 이하이어야 한다.
+다) 변류기는 직류 500[V]의 절연저항계로 시험을 하는 경우 5[㏁] 이상이어야 한다. 이때 측정위치 3곳을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 1[A] 이하
+나) 5
+다)
+ ① 절연된 1차 권선과 2차 권선
+ ② 절연된 1차 권선과 외부금속부
+ ③ 절연된 2차 권선과 외부금속부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예비전원설비로 이용되는 축전지에 대한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 자기방전량만을 항상 충전하는 방식의 명칭을 쓰시오.
+나) 비상용 조명부하 200[V]용, 50[W] 80등, 30[W] 70등이 있다. 방전시간은 30분이고, 축전지는 HS형 110cell이며, 허용최저전압은 190[V], 최저축전지온도가 5℃일 때 축전지용량[Ah]을 구하시오. (단, 경년용량저하율은 0.8, 용량환산시간은 1.2[h] 이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 세류충전방식
+다) 연축전지 : 2[V], 알칼리축전지 : 1.2[V]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 도면을 보고 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) ㉮는 수동으로 화재신호를 발신하는 P형 발신기세트이다. 발신기세트와 수신기 간의 배선실이가 15[m]인 경우 전선은 총 몇 [m]가 필요한지 산출하시오. (단, 층고, 할증 및 여유율 등은 고려하지 않는다.)
+나) 상기 건물에 설치된 감지기가 2종인 경우 8개의 감지기가 최대로 감지할 수 있는 감지구역의 바닥면적[m²]합계를 구하시오. (단, 천장높이는 5[m]인 경우이다.)
+다) 감지기와 감지기 간, 감지기와 P형 발신기셑  간의 길이가 각각 10[m]인 경우 전선관 및 전선물량을 산출과정과 함께 쓰시오. (단 층고, 할증 및 여유율 등은 고려하지 않는다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240304(1
+240304(2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240304a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3상 380[V] 전전압기동시 기동전류 135[A], 기동토크 150[%]인 전동기가 있다. 이 전동기를 Y-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 기동할 경우 기동전류와 기동토크를 구하시오.</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1271,7 +1676,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1282,6 +1687,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2990,7 +3398,9 @@
       <c r="C19" s="1">
         <v>5</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" s="4">
+        <v>240118</v>
+      </c>
       <c r="F19" s="1" t="s">
         <v>169</v>
       </c>
@@ -3036,8 +3446,260 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D19" s="2"/>
+    <row r="2" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="1">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1">
+        <v>240201</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="1">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1">
+        <v>240203</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="243.6" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="1">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1">
+        <v>240204</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1">
+        <v>240205</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="313.2" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C15" s="1">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C16" s="1">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C17" s="1">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1">
+        <v>240216</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C18" s="1">
+        <v>8</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5</v>
+      </c>
+      <c r="D19" s="4">
+        <v>240218</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>238</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3080,6 +3742,85 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="1">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1">
+        <v>240301</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" s="1">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1">
+        <v>240101</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C4" s="1">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1">
+        <v>240303</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" s="1">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+    </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D19" s="2"/>
     </row>

--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="405" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B52A4CB-B459-4F0B-BC63-BF985F57318C}"/>
+  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7508290A-27B5-4099-AB9F-4ADE5661E552}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
@@ -1562,11 +1562,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>240304(1
-240304(2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>240304a</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1595,6 +1590,11 @@
       </rPr>
       <t xml:space="preserve"> 기동할 경우 기동전류와 기동토크를 구하시오.</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240304(1,
+240304(2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1676,7 +1676,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1687,9 +1687,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3398,7 +3395,7 @@
       <c r="C19" s="1">
         <v>5</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="1">
         <v>240118</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -3694,7 +3691,7 @@
       <c r="C19" s="1">
         <v>5</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="1">
         <v>240218</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -3804,10 +3801,10 @@
         <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>250</v>
@@ -3815,7 +3812,7 @@
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>

--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7508290A-27B5-4099-AB9F-4ADE5661E552}"/>
+  <xr:revisionPtr revIDLastSave="480" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44339450-DF1E-4D87-A222-513EA2359A31}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="25년 3회" sheetId="3" r:id="rId3"/>
     <sheet name="24년 1회" sheetId="5" r:id="rId4"/>
     <sheet name="24년 2회" sheetId="6" r:id="rId5"/>
-    <sheet name="24년 3회(작성중)" sheetId="7" r:id="rId6"/>
+    <sheet name="24년 3회" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="285">
   <si>
     <t>문제</t>
   </si>
@@ -1595,6 +1595,190 @@
   <si>
     <t>240304(1,
 240304(2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상조명등의 설치기준에 관한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 다음 빈칸을 완성하시오.
+ - 조도는 비상조명등이 설치된 장소의 각 부분의 바닥에서 ( ① )[lx] 이상이 되도록 할 것
+ - 예비전원을 내장하는 비상조명등에는 평상시 점등 여부를 확인할 수 있는 ( ② )를 설치하고 해당 조명등을 유효하게 작동시킬 수 있는 용량의 축전지와 예비전원 충전장치를 내장할 것
+나) 예비전원을 내장하지 않은 비상조명등의 비상전원 설치기준 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 
+① 1[lx]
+② 점검스위치
+나) 
+① 점검에 편리하고 화재 및 침수 등의 재해로 인한 피해를 받을 우려가 없는 곳에 설치할 것
+② 상용전원으로부터 전력공급이 중단된 때에는 자동으로 비상전원으로부터 전력공급을 받을 수 있도록 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*비상조명 설치기준
+① 특정소방대상물의 각 거실과 그로부터 지상에 이르는 복도ㆍ계단 및 그 밖의 통로에 설치할 것
+② 조도는 비상조명등이 설치된 장소의 각 부분의 바닥에서 1[lx] 이상이 되도록 할 것
+③ 예비전원을 내장하는 비상조명등에는 평상시 점등 여부를 확인할 수 있는 점검스위치를 설치하고 해당 조명등을 유효하게 작동시킬 수 있는 용량의 축전지와 예비전원 충전장치를 내장할 것
+④ 비상전원은 비상조명등을 20분 이상 유효하게 작동시킬 수 있는 용량으로 할 것
+⑤ 예비전원을 내장하지 않은 비상조명등의 비상전원은 자기발전설비, 축전지설비 또는 전기저장장치를 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연기감지기에대한 사항이다. 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 광전식 스포트형 감지기(산란광식)의 작동원리를 쓰시오.
+나) 광전식 분리형 감지기(감광식)의 작동원리를 쓰시오.
+다) 광전식 스포트형 감지기의 적응장소 2가지를 쓰시오.(단, 환경은 연기가 멀리 이동해서 감지기에 도달하는 장소로 한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 화재발생시 연기입자에 의해 난반사된 빛이 수광부 내로 들어오는 것을 감지
+나) 화재발생시 연기입자에 의해 수광부의 수광량이 감소하므로 이를 검출하여 화재신호 발신
+다)
+ ① 계단ㆍ경사로
+ ② 복도ㆍ통로
+ ③ 엘리베이터 승상로
+ ④ 린넨슈트
+ ⑤ 파이프피트 및 덕트
+ ⑥ 전산실
+ ⑦ 통신기기실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 국가화재안전기준에서 정하는 옥내소화전설비의 전원 및 비상전원 설치기준에 대한 설명이다. (   )안에 알맞은 용어를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ비상전원은 옥내소화전설비를 유효하게 ( ① )분 이상 작동할 수 있어야 한다.
+ㆍ비상전원을 실내에 설치하는 때에는 그 실내에 ( ② )을 설치하여야 한다.
+ㆍ상용전원이 저압수전인 경우에는 ( ③ )의 직후에서 분기하여 전용 배선으로 하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 20
+② 비상조명등
+③ 인입개폐기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어떤 건물의 사무실 바닥면적이 700[m²]이고, 천장높이가 4[m]로서 내화구조이다. 이 사무실에 차동식 스포트형(2종) 감지기를 설치하려고 한다. 최소 몇 개가 필요한지 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(350/35)+(350/35) = 20[개]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 단독경보형 감지기의 설치기준이다. (  ) 안에 알맞은 내용을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가) 각 실마다 설치하되, 바닥면적이 ( ① )[m²]를 초과하는 경우에는 ( ② )[m²]마다 1개 이상 설치하여야 한다.
+나) 이웃하는 실내의 바닥면적이 각각 ( ③ )[m²] 미만이고, 벽체의 상부의 전부 또는 일부가 개방되어 이웃하는 실내와 공기가 상호 유통되는 경우에는 이를 ( ④ )개의 실로 본다. 
+다) 최상층의 ( ⑤ )의 천장(외기가 상통하는 ( ⑥ )의 경우 제외)에 설치할 것
+라) 상용전원을 주전원으로 사용하는 단독경보형 감지기의 ( ⑦ )는 법 제 40조에 따라 제품검사에 합격한 것을 사용할 것 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 150
+② 150
+③ 30
+④ 1
+⑤ 계단실
+⑥ 계단실
+⑦ 2차 전지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두 대의 전동기가 전부하시 각각 출력 8[kW], 출력, 2[kW]이고, 효율이 80[%]이다. 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가)  출력 8[kW], 출력, 2[kW] 전동기의 동손의 관계를 구하시오.
+나) 철손[kW]과 동손[kW]을 각각 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방시설 설치 및 관리에 관한 법령상 소방시설 중 경보설비의 종류 8가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 자동화재탐지설비
+② 시각경보기
+③ 자동화재속보설비
+④ 누전경보기
+⑤ 가스누설경보기
+⑥ 비상방송설비
+⑦ 비상경보설비
+⑧ 단독경보형 감지기
+⑨ 화재알림설비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가로 15[m] 세로 5[m]인 특정소방대상물에 이산화탄소 소화설비를 설치하려고 한다. 연기감지기의 최소 설치개수를 구하시오. (단, 감지기의 부착높이는 3[m]이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ(15×5)/150 = 0.5 =1개
+-&gt; 1개×2회로 =2개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정소방대상물에 설치된 소방시설 등을 구성하는 전부 또는 일부를 개설, 이전 또는 정비하는 소방시설공사의 착공신고 대상 3가지를 쓰시오. (단, 고장 또는 파손 등으로 인하여 작동시킬 수 없는 소방시설을 긴급히 교체하거나 보수하여야 하는 경우에는 신고하지 않을 수 있다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 수신반
+② 소화펌프
+③ 동력제어반
+④ 감시제어반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역률 80[%], 용량100[kVA]의 유도전동기가 있다. 여기에 역률 60[%], 용량 50[kVA]의 전동기를 추가로 설치하고, 전동기 합성 역률을 90[%]로 개선하고자 할 경우 필요한 전력용 콘덴서의 용량[kVA]을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 그림은 브리지 회로를 나타낸다. 평형조건이 만족할 때 R₂를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240316a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국전기설비규정(KEC)에서 규정하는 금속관공사의 시설조건에 관한 (   )안에 알맞은 말을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ전선은 절연전선(( ① )제외)일 것
+ㆍ전선은 ( ② )일 것, 단, 다음의 것은 적용하지 않는다.
+ - 짧고 가는 금속관에 넣은 것
+ - 단면적 ( ③ )[mm²](알루미늄선은 단면적 ( ④ )[mm²]) 이하의 것
+ㆍ전선은 금속관 안에서 ( ⑤ )이 없도록 할 것
+ㆍ관의 끝 부분에는 전선의 피복을 손상하지 않도록 ( ⑥ )을 사용할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 옥외용 비닐절연전선
+② 연선
+③ 10
+④ 16
+⑤ 접속점
+⑥ 부싱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비 수신기의 동시작동시험의 목적을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ감지기회로가 동시에 수회선 작동하더라도 수신기의 기능에 이상이 없는지 여부 확인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1648,18 +1832,12 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1676,17 +1854,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3054,7 +3235,7 @@
       <c r="C15" s="1">
         <v>8</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="2"/>
       <c r="E15" s="1" t="s">
         <v>170</v>
       </c>
@@ -3817,9 +3998,180 @@
       <c r="C6" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D19" s="2"/>
+      <c r="D6" s="1">
+        <v>240305</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C8" s="1">
+        <v>6</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9" s="1">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12" s="1">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1">
+        <v>240311</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1">
+        <v>240313</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C15" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C16" s="1">
+        <v>6</v>
+      </c>
+      <c r="D16" s="1">
+        <v>240315</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1">
+        <v>240316</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C19" s="1">
+        <v>3</v>
+      </c>
+      <c r="D19" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="480" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44339450-DF1E-4D87-A222-513EA2359A31}"/>
+  <xr:revisionPtr revIDLastSave="617" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58997A8F-9519-4721-8501-4A408336578B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="25년 1회" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="24년 1회" sheetId="5" r:id="rId4"/>
     <sheet name="24년 2회" sheetId="6" r:id="rId5"/>
     <sheet name="24년 3회" sheetId="7" r:id="rId6"/>
+    <sheet name="23년 1회" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="335">
   <si>
     <t>문제</t>
   </si>
@@ -1781,12 +1782,306 @@
     <t>ㆍ감지기회로가 동시에 수회선 작동하더라도 수신기의 기능에 이상이 없는지 여부 확인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>에비전원설비로 이용되는 축전지에 대한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 보수율의 의미를 쓰고, 그 것을 산정하는 값은 보통 얼마인지 쓰시오.
+나) 연축전지와 알칼리 축전지의 공칭전압[V]을 쓰시오.
+다) 최저허용전압이 1.06[V/cell]일 때 축전지용량[Ah]을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 부하를 만족하는 용량을 감정하기 위한 계수, 0.8
+나) 연축전지 : 2[V], 알칼리축전지 : 1.2[V]
+다) C=(1/0.8)×(0.85×20+0.45×45+0.24×70)=67.56[Ah]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240101a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가스누설경보기에 관한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 가스의 누설을 표시하는 표시등 및 가스가 누설된 경계구역의 위치를 표시하는 표시등은 등이 켜질 때 어떤 색으로 표시되어야 하는가?
+나) 가스누설경보기는 구조에 따라 무슨 형과 무슨 형으로 구분하는가?
+다) 가스누설경보기 중 가스누설을 검지하여 중계기 또는 수신부에 가스누설의 신호를 발신하는 부분 또는 가스누설을 검지하여 이를 음향으로 경보하고 동시에 중계기 또는 수신부에 가스누설의 신호를 발신하는 부분은 무엇인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 황색
+나) 단독형, 분리형
+다) 탐지부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시각경보기를 설치하여야 하는 특정소방대상물을 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 근린 생활
+② 문화 및 집회시설
+③ 종교시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가) 피난구유도등을 설치해야 되는 장소의 기준 3가지만 쓰시오.
+나) 피난구유도등은 피난구의 바닥으로부터 높이 몇 [m] 이상의 곳에 설치하여야 하는가?
+다) 피난구유도등 표시면의 색상은? 
+ - 바탕색 :
+ - 글자색 : </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가)
+ - 직통계산ㆍ직통계단의 계단실 및 그 부속실의 출입구
+ - 출입구에 이르는 복도 또는 통로로 통하는 출입구
+ - 안전구획된 거실로 통하는 출입구
+나) 1.5m 이상
+다)
+ - 바탕색 : 녹색
+ - 글자색 : 백색</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복도통로유도등의 설치기준을 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 복도에 설치하되 피난구유도등이 설치된 출입구의 맞은편 복도에는 입체형으로 설치하거나, 바닥에 설치
+② 구부러진 모퉁이 및 통로유도등을 기점으로 보행거리 20[m]마다 설치
+③ 바닥으로부터 높이 1[m] 이하의 위치에 설치
+④ 바닥에 설치하는 통로유도등은 하중에 따라 파괴되지 않는 강도의 것으로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상콘센트설비의 설치기준에 관해 다음 빈칸을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 10
+② 3
+③ 3
+④ 내화배선
+⑤ 내열배선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ하나의 전용회로에 설치하는 비상콘센트는 ( ① )개 이하로 할 것. 이 경우 전선의 용량은 각 비상콘센트[비상콘센트가 ( ② )개 이상인 경우에는 ( ③ )개]의 공급용량을 합한 용량 이상의 것으로 해야 한다.
+ㆍ전원회로의 배선은 ( ④ )으로, 그 밖의 배선은 ( ④ ) 또는 ( ⑤ )으로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상콘센트의 설치기준에 대한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 비상콘센트설비의 정의를 쓰시오.
+나) 전원회로의 공급용량은 몇 [kVA] 이상인지 쓰시오.
+다) 플러그 접속기의 칼받이 접지극에 하는 접지공사의 종류를 쓰시오.
+라) 220[V] 전원에 1[kW] 송풍기를 연결하여 운전하는 경우 회로에 흐르는 전류 [A]를 구하시오. (단, 역률은 90[%]이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 화재시 소화활동 등에 필요한 전원을 전용회선으로 공급하는 설비
+나) 1.5[kVA]
+다) 보호접지
+라) (1×10³)/220×0.9 = 5.05[A]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유량 5[m³/min], 양정 30[m]인 펌프전동기의 용량[kW]을 계산하시오. (단, 효율 : 0.72, 전달계수 : 1.25)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ㆍ(9.8×1.25×30×5)/(0.72×60)=42.534=42.53[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>𝑘𝑊]</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 P형 수신기와 R형 수신기의 기능을 각각 2가지씩 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) P형 수신기 기능
+ ① 화재표시 작동시험장치
+ ② 수신기와 감지기 사이의 도통시험장치
+ ③ 상용전원과 예비전원의 자동절환장치
+ ④ 예비전원 양부시험장치
+ ⑤ 기록장치
+나) R형 수신기의 기능
+ ① 화재표시 작동시험장치
+ ② 수신기와 중계기 사이의 단선ㆍ지락ㆍ도통시험장치
+ ③ 상용전원과 예비전원의 자동절환장치
+ ④ 예비전원 양부시험장치
+ ⑤ 기록장치
+ ⑥ 지구등 또는 적당한 표시장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 그림과 같이 차동식 스포트형 감지기 A, B, C, D가 있다. 배선을 전부 송배선식으로 할 경우 박스와 감지기 "C" 사이의 배선 가닥수는 몇 가닥인가? (단, 배선상의 유효한 조치를 하고, 전화선은 삭제한다.)
+나) 차동식 분포형 감지기의 공기관의 재질을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 4가닥
+나) 중공동관</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 비상조명등의 설치기준에 관한 사항이다. 다음 (  )안을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ예비전원을 내장하는 비상조명등에는 평상시 점등 여부를 확인할 수 있는 ( ① )를 설치하고 해당 조명등을 유효하게 작동시킬 수 있는 용량의 ( ② )와 ( ③ )를 내장할 것
+ㆍ비상전원은 비상조명등을 ( ④ )분 이상 유효하게 작동시킬 수 있는 용량으로 할 것. 다만, 다음의 특정소방대상물의 경우에는 그 부분에서 피난층에 이르는 부분의 비상조명등을 ( ⑤ )분 이상 유효하게 작동시킬 수 있는 용량으로 하여야 한다. 
+ - 지하층을 제외한 층수가 11층 이상의 층
+ - 지하층 또는 무창층으로서 용도가 도매시장ㆍ소매시장ㆍ여객자동차터미널ㆍ지하역사 또는 지하상가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 점검스위치
+② 축전지
+③ 예비전원 충전장치
+④ 20
+⑤ 60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음에서 설명하는 감지기의 명칭을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 비화재보 방지가 주목적으로 감지원리 동일하나 성능, 종별, 공칭작동온도, 공칭축적시간이 다른 감지소자의 조합으로 된 것이며, 1개의 감지기 내에 서로 다른 종별 또는 감도 등의 기능을 갖춘 것으로서 일정 시간 간격을 두고 각각 다른 2개 이상의 화재신호를 발하는 감지기
+나) 주위의 온도 또는 연기의 양의 변화에 따른 화재정보신호값을 출력하는 방식의 감지기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 다신호식 감지기
+나) 아날로그식 감지기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상경보설비 및 단독경보형 감지기, 비상방송설비의 설치기준에 관한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 비상벨설비 또는 자동식 사이렌설비의 설치높이[m]를 쓰시오.
+나) 단독경보형 감지기의 설치장소의 면적이 600[m²]일 때 감지기 개수를 구하시오.
+다) 비상방송설비에서 증폭기의정의를 쓰시오.
+라) 비상방송설비에서 층수가 지하 2층, 지상 7층인 건물에서 5층의 배선이 단락되어도 화재통보에 지장이 없어야 하는 층은 몇 층인지 모두 쓰시오.(단, 각 층에 배선상 유효한 조치를 하였다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 바닥에서 0.8[m] 이상 1.5[m] 이하
+나) 600/150 = 4개
+다) 전압ㆍ전류의 진폭을 늘려 감도를 좋게 하고 미약한 음성전류를 커다란 음성전류로 변화시켜 소리를 크게 하는 장치
+라) 지하 1~2층, 지상 1~4층, 지상 6~7층</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예비전원설비에 대한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 축전지의 과방전 또는 방치상태에서 기능회복을 위하여 실시하는 충전방식은 무엇인지 다음 보기에서 고르시오.
+ [보기] : 균등충전, 부동충전, 세류충전, 회복충전
+나) 부동충전방식에 대한 회로(개략도)를 그리시오.
+다) 연축전지의 정격용량은 250[Ah]이고, 상시부하가 8[kW]이며 표준전압이 100[V]인 부동충전방식의 충전기 2차 충전전류는 몇 A인지 구하시오. (단, 축전지의 방전율은 10시간율로 한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 회복충전
+나) 그림 참조
+다) (250/10)+(8×10³/100)=105[A]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상방송설비의 설치기준에 관한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 음량조절기의 정의를 쓰시오.
+나) 확성기는 각 층마다 설치하되, 그 층의 각 부분으로부터 하나의 확성기까지 수평거리는 몇 [m]이하로 해야 하는가?
+다) 음량조정기를 설치하는 경우 음량조정기의 배선은 몇 선식으로 해야 하는가?
+라) 확성기의 음성입력은 실내에 설치하는 것에 있어서는 몇 [W] 이상으로 설치해야 하는가?
+마) 기동장치에 따른 화재신고를 수신한 후 필요한 음량으로 화재발생 상황 및 피난에 유효한 방송이 자동으로 개시될 때까지의 소요시간은 몇 초 이내로 하여야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 가변저항을 이용하여 전류를 변화시켜 음량을 크게 하거나 작게 조절할 수 있는 장치
+나) 25[m]
+다) 3선식
+라) 1[W]
+마) 10초</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무선통신보조설비의 설치기준에 관한 다음 물음에 답을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 누설동축케이블의 끝부분에는 무엇을 견고하게 설치하여야 하는가?
+나) 누설동축케이블은 화재에 의하여 해당 케이블의 피복이 소실될 경우에 케이블 본체가 떨어지지 않도록 하기 위하여 몇 m 이내마다 금속제 또는 자기제 등의 지지금구로 고정시켜야 하는가?
+다) 누설동축케이블 및 안테나는 고압의 전로로부터 몇 [m] 이상 떨어진 위치에 설치해야 하는가? (단, 해당 전로에 정전기차폐장치를 설치하지 않았다.)
+라) 증폭기의 전면에는 주회로의 전원이 정상인지의 여부를 표시할 수 있는 것으로서 무엇을 설치하여야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 무반사 종단저항
+나) 4[m]
+다) 1.5[m]
+라) 표시등, 전압계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 자동화재탐지설비의 P형 수신기의 미완성 결선도를 완성하시오. (단, 발신기에 설치된 단자는 왼쪽으로부터 응답, 지구공통, 지구이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림과 같이 소방부하가 연결된 회로가 있다. A점과 B점의 전압은 몇 [V]인가? (단, 공급전압은 100[V] 이며, 단상 2선식이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230117a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230118a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230110a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230118(1, 230118(2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1831,6 +2126,12 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1854,7 +2155,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1867,8 +2168,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4171,11 +4475,304 @@
       <c r="C19" s="1">
         <v>3</v>
       </c>
-      <c r="D19" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08E9414D-3FA5-419B-9C17-D6357D27FB54}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="49.59765625" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>296</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="83.4" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>230108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>306</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5">
+        <v>230110</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>314</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>317</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>230114</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>323</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>326</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18" s="5">
+        <v>230117</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>334</v>
+      </c>
+      <c r="E19" t="s">
+        <v>332</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="617" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58997A8F-9519-4721-8501-4A408336578B}"/>
+  <xr:revisionPtr revIDLastSave="725" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAE0CFE3-88EC-45C3-9B0A-AA1A67769ADA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="25년 1회" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="24년 2회" sheetId="6" r:id="rId5"/>
     <sheet name="24년 3회" sheetId="7" r:id="rId6"/>
     <sheet name="23년 1회" sheetId="8" r:id="rId7"/>
+    <sheet name="23년 2회" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="381">
   <si>
     <t>문제</t>
   </si>
@@ -2074,6 +2075,247 @@
   </si>
   <si>
     <t>230118(1, 230118(2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비 P형 수신기 1경계구역에 대한 배선의 용도를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 경종선
+② 경종표시등공통선
+③ 표시등선
+④ 응답선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 가스계 소화설비의 수동조작함
+나) 프리액션밸브 수동조작함
+다) 소화가스패키지
+라) 증폭기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 상용전원 정전시 예비전원으로 절환하고 상용전원 복구시 예비전원에서 상용전원으로 절환하여 운전하는 시퀀스제어회로의 미완성도이다. 시퀀스제어도를 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방설비 배선공사에 사용되는 부품의 명칭을 적으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230204a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 부싱
+② 커플링
+③ 노멀밴드
+④ 유니버설엘보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분전반에서 60[m]의 거리에 220[V], 전력 2.2[kW] 단상 2선식 전기히터를 설치하려고 한다. 전선의 굵기는 몇 [mm²]인지 계산상의 최소 굵기를 구하시오. (단 전압강하는 1[%] 이내이고, 전선은 동선을 사용한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광원점등방식의 피난유도선 설치기준 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 구획된 각 실로부터 주출입구 또는 비상구까지 설치
+② 피난유도 표시부는 바닥으로부터 높이 1[m] 이하의 위치 또는 바닥면에 설치
+③ 비상전원이 상시 충전상태를 유지하도록 설치
+④ 피난유도 표시부는 50[cm] 이내의 간격으로 연속되도록 설치하되 실내장식물 등으로 설치가 곤란할 경우 1[m] 이내로 설치
+⑤ 수신기로부터의 화재보호 및 수동조작에 의하여 광원이 점등되도록 설치
+⑥ 바닥에 설치되는 피난유도 표시부는 매립하는 방식을 사용
+⑦ 피난유도 제어부는 조작 및 관리가 용이하도록 바닥으로부터 0.8~1.5[m] 이하의 높이에 설치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 보기는 제연설비에서 제연구역을 구획하는 기준을 나열한 것이다. ① ~ ⑤까지의 빈칸을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 하나의 제연구역의 면적은 ( ① ) 이내로 한다.
+나) 통로상의 제연구역은 보행중심선의 길이가 ( ② )를 초과하지 않아야 한다.
+다) 하나의 제연구역은 직경 ( ③ ) 원 내에 들어갈 수 있도록 한다.
+라) 하나의 제연구역은 ( ④ )개 이상의 층에 미치지 않도록 한다. (단, 층의 구분이 불분명한 부분은 다른 부분과 별도로 제연구획할 것)
+마) 재질은 ( ⑤ ), ( ⑥ ) 또는 제연경계벽으로 성능을 인정받은 것으로서 화재시 쉽게 변형ㆍ파괴되지 아니하고 연기가 누설되지 않는 기밀성 있는 재료로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 1000[m²]
+② 60[m]
+③ 60[m]
+④ 2
+⑤ 내화재료
+⑥ 불연재료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 표는 소화설비별로 사용할 수 있는 비상전원의 종류를 나타낸 것이다. 각 소화설비별로 설치하여야 하는 비상전원을 찾아 빈칸에 O표 하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230208a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무선통신보조설비에 사용되는 분배기, 분파기, 혼합기의 기능에 대하여 간단하게 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ㆍ분배기 : 
+ㆍ분파기 : 
+ㆍ혼합기 : </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ분배기 : 신호의 전송로가 분기되는 장소에 설치하는 것으로 임피던스 매칭과 신호균등분배를 위해 사용하는 장치
+ㆍ분파기 : 서로 다른 주파수의 합성된 신호를 분리하기 위해서 사용하는 장치
+ㆍ혼합기 : 두 개 이상의 입력신호를 원하는 비율로 조합한 출력이 발생하도록 하는 장치
+ㆍ증폭기 : 신호전송시 신호가 약해져 수신이 불가능해지는 것을 방지하기 위해서 증폭하는 장치
+ㆍ누설동축케이블 : 동축케이블의 외부도체에 가느다란 홈을 만들어서 전파가 외부로 새어나갈 수 있도록 한 케이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감지기회로의 배선에 대한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 송배선식에 대하여 설명하시오.
+나) 교차회로의 방식에 대하여 설명하시오.
+다) 교차회로방식의 적용설비 2가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 도통시험을 용이하게 하기 위해 배선의 도중에서 분기하지 않는 방식
+나) 하나의 담당구역 내에 2 이상의 감지기회로를 설치하고 2 이상의 감지기회로가 동시에 감지되는 때에 설비가 작동하는 방식
+다) 
+ - 분말소화설비
+ - 할론소화설비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비와 스프링클러설비 프리액션밸브의 간선계통이다. 다음 각 물음에 답하시오. (단, 프리액션밸브용 감지기공통선관 전원공통선은 분리해서 사용하고 압력스위치, 탬퍼스위치 및 솔레노이드밸브용 공통선은 1가닥을 사용하는 조건이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) ㉮ ~ ㉸까지의 배선 가닥수를 쓰시오. (단, 전화선은 삭제한다.)
+나) ㉲의 배선별 용도를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230202a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230201a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230203a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230211a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연축전지가 여러 개 설치된 축전지설비가 있다. 비상용 조명부하가 6[kW]이고, 표준전압이 100[V]라고 할 때 다음 각 물음에 답하시오. (단, 축전징에 1셀의 여유를 둔다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 연축전지는 몇 셀 정도 필요한가?
+나) 분비물이 혼입된 납축전지를 방전상태로 오랫동안 방치해두면 극판의 황산납이 회백색으로 변하며 내부저항이 증가하고 전지의 용량이 감소하며 수명을 단축시키는 현상을 무엇이라고 하는가?
+다) 충전시에 발생하는 가스의 종류는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) (100/2)+1 = 51[셀]
+나) 셀페이션 현상
+다) 수소가스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 화재안전기준에서 정한 연기감지기의 설치기준이다. 다음 괄호 안 ① ~ ⑧에 알맞은 답을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 부착높이에 따른 기준
+나) 감지기는 복도 및 통로에 있어서는 보행거리 ( ④ )[m](3종에 있어서는 ( ⑤ )[m])마다, 계단 및 경사로에 있어서는 수직거리 ( ⑥ )[m](3종에 있어서는 ( ⑦ )[m])마다 1개 이상으로 할 것
+다) 감지기는 벽 또는 보로부터 ( ⑧ )[m] 이상 떨어진 곳에 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 
+① 150
+② 50
+③ 20
+나) 
+④ 30
+⑤ 20
+⑥ 15
+⑦ 10
+다)
+⑧ 0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230213a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내화구조인 건물에 차동식 스포트형 2종 감지기를 설치할 경우 다음 각 물음에 답하시오. (단, 감지기가 부착되어 있는 천장의 높이는 3.8m이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 다음 각 실에 필요한 감지기의 수량을 산출하시오.
+나) 실 전체의 경계구역수를 선정하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230214a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음의 무접점회로를 보고 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 무접점회로를 간소화된 논리식으로 표현하시오.
+나) 간소화된 논리회로의 무접점회로를 그리시오.
+다) 간소화된 논리회로의 유접점회로를 그리시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230215a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비를 설치해야 할 특정소방대상물(연면적, 바닥면적 등의 기준)에 대한 다음 (  )안을 완성하시오. (단, 전부 필요한 경우는 '전부'라고 쓰고, 필요 없는 경우에는 '필요 없음' 이라고 답 할 것)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230216a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림과 같은 건물평면도의 경우 자동화재탐지설비의 최소경계구역의 수를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230217a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P형 수신기와 감지기와의 배선회로에서 배선저항은 50[Ω], 릴레이저항은 1000[Ω], 감시상태의 감시전류는 2[mA]이다. 회로전압이 DC 24V 일 때 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 종단저항값[Ω]을 구하시오.
+나) 감지기가 동작할 때(화재시)의 전류는 몇 [mA]인가?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2171,8 +2413,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4646,10 +4888,10 @@
       <c r="C11">
         <v>5</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11">
         <v>230110</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" t="s">
         <v>333</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -4750,10 +4992,10 @@
       <c r="C18">
         <v>6</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18">
         <v>230117</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" t="s">
         <v>331</v>
       </c>
     </row>
@@ -4769,6 +5011,316 @@
       </c>
       <c r="E19" t="s">
         <v>332</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5743C26-ABAE-4024-86B8-68A80D5490B2}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="49.59765625" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2" s="5">
+        <v>230201</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C3" s="4">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
+        <v>230202</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5">
+        <v>230203</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C5" s="4">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>230204</v>
+      </c>
+      <c r="E5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C6" s="4">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>230205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C7" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C8" s="4">
+        <v>5</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C9" s="4">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>230208</v>
+      </c>
+      <c r="E9" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C10" s="4">
+        <v>6</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C11" s="4">
+        <v>5</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C12" s="4">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>230211</v>
+      </c>
+      <c r="E12" t="s">
+        <v>361</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C13" s="4">
+        <v>6</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C14" s="4">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>368</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C15" s="4">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>230214</v>
+      </c>
+      <c r="E15" t="s">
+        <v>371</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C16" s="4">
+        <v>8</v>
+      </c>
+      <c r="D16">
+        <v>230215</v>
+      </c>
+      <c r="E16" t="s">
+        <v>374</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C17" s="4">
+        <v>5</v>
+      </c>
+      <c r="D17">
+        <v>230216</v>
+      </c>
+      <c r="E17" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C18" s="4">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>230217</v>
+      </c>
+      <c r="E18" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C19" s="4">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>230218</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="725" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAE0CFE3-88EC-45C3-9B0A-AA1A67769ADA}"/>
+  <xr:revisionPtr revIDLastSave="842" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C2EA8C6-CD8F-4F77-B751-14E6DDAFA40E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="8" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="25년 1회" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="24년 3회" sheetId="7" r:id="rId6"/>
     <sheet name="23년 1회" sheetId="8" r:id="rId7"/>
     <sheet name="23년 2회" sheetId="9" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="429">
   <si>
     <t>문제</t>
   </si>
@@ -2318,12 +2319,375 @@
 나) 감지기가 동작할 때(화재시)의 전류는 몇 [mA]인가?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>감지기회로의 배선방식으로 교차회로방식을 사용할 경우 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 불대수의 정리를 이용하여 간단한 논리식을 쓰시오.
+나) 무접점회로로 나타내시오.
+다) 진리표를 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>피난유도선은 햇빛이나 전등불에 따라 축광하거나 전류에 따라 빛을 발하는 유도체로서, 어두운상태에서 피난을 유도할 수 있도록 띠형태로 설치되는 피난유도시설이다. 광원점등방식의 피난유도선의 설치기준 5가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정온식 스포트형 감지기의 열감지방식 5가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 바이메탈의 활곡 이용
+② 바이메탈의 반전 이용
+③ 금속의 팽창계수차 이용
+④ 액체(기체)의 팽창 이용
+⑤ 가용절연물 이용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 그림과 같은 회로에서 부하 R_L에서 소비되는 최대전력에 대한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 최대전력전달 조건을 쓰시오.
+나) 최대전력식을 유도하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>높이 20[m] 이상되는 곳에 설치할 수 있는 감지기를 2가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 불꽃감지기
+② 광전식(분리형, 공기흡입형) 중 아날로그방식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상조명등의 설치기준에 관한 다음 (  )안을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">비상조명등의 비상전원은 비상조명등을 20분 이상 유효하게 작동시킬 수 있는 용량으로 할 것. 다만, 다음의 특정소방대상물의 경우에는 그 부분에서 피난층에 이르는 부분의 비상조명등을 ( ① )분 이상 유효하게 작동시킬 수 있는 용량으로 하여야 한다.
+ - ② 
+ - ③ </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 60분
+② 지하층을 제외한 층수가 11층 이상의 층
+③ 지하층 또는 무창층으로서 용도가 도매시장ㆍ소매시장ㆍ여객자동차터미널ㆍ지하역사 또는 지하상가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 건물의 평면도를 나타낸 것으로 거실에는 차동식 스포트형 감지기 1종, 복도에는 연기감지기 2종을 설치하고자 한다. 감지기의 설치높이는 3.8[m]이고 내화구조이며, 복도의 보행거리는 50[m]이다. 각 실에 설치될 감지기의 개수를 계산하시오. (단, 계산식을 화용하여 설치수량을 구하시오.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>극수변환식 3상 농형 유도전동기가 있다. 고속측은 4극이고 정격출력은 90[kW]이다. 저속측은 1/3속도라면 저속측의 극수와 정격출력은 몇 [kW]인지 계산하시오. (단, 슬립 및 정격토크는 저속측과 고속측이 같다고 본다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 극수 :
+나) 정격출력[kW] :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무선통신보조설비의 누설동축케이블의 기호를 보기에서 찾아쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">①LCX - ②FR - ③SS - ④20 ⑤D - ⑥14 ⑦6
+[보기] 사용주파수, 특성임피던스, 절연체 외경, 자기지지, 난연성(내열성), 누설동축케이블 
+예) ⑦ 결합손실 표시 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 누설동축케이블
+② 난연성(내열성)
+③ 자기지지
+④ 절연체 외경
+⑤ 특성임피던스
+⑥ 사용주파수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 평면을 나타낸 도면이다. 이 도면을 보고 다음 각 물음에 답하시오. (단, 각 실은 이중천장이 없는 구조며, 전선관은 16[mm] 후강스틸전선관을 사용콘크리트 내 매입 시공한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 시공에 소요되는 로그너트와 부싱의 소요개수는?
+ - 로크너트 : 
+ - 부싱 :
+나) 각 감지기간과 감지기와 수동발신기세트(①~⑤) 간에 배선되는 전선의 가단수는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 
+ - 로크너트 : 44개
+ - 부싱 : 22개
+나) ① 2가닥, ② 4가닥, ③ 2가닥, ④ 4가닥, ⑤ 2가닥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무선통신보조설비의 설치기준에 관한 다음 물음에 답 또는 빈칸을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 증폭기의 정의를 쓰시오.
+나) 증폭기에는 비상전원이 부착된 것으로 하고 해당 비상전원의 용량은 무선통신보조설비를 유효하게 ( ① )분 이상 작동시킬 수 있는 것으로 할 것
+다) 증폭기의 전면에는 주회로의 전원이 정상인지의 여부를 표시할 수 있는 ( ② ) 및 ( ③ )를 설치할 것
+라) 증폭기의 전원은 전기가 정상적으로 공급되는 ( ④ ), ( ⑤ ) 또는 ( ⑥ )으로 하고, 전원까지의 배선은 전용으로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 신호전송시 신호가 약해져 수신이 불가능해지는 것을 방지하기 위해서 증폭하는 장치
+① 30분
+② 표시등
+③ 전압계
+④ 축전지설비
+⑤ 전기저장장치
+⑥ 교류전압 옥내간선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비 및 시각경보장치의 화재안전기술기준에 따른 배선에 대한 내용이다. 다음 (  )안을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ아날로그식, 다신호식 감지기나 R형 수긴기용으로 사용되는 것은 ( ① ) 방해를 받지않는 실드선 등을 사용해야 하며, 광케이블의 경우에는 전자파 방해를 받지 아니하고 내열성능이 있는 경우 사용할 것. 다만, 전자파 방해를 받지 않는 방식의 경우에는 그렇지 않다.
+ㆍ감지기 사이의 회로의 배선은 ( ② )으로 할 것
+ㆍ전원회로의 전로와 대지 사이 및 배선 상호간의 절연저항은 「전기사업법」 제67조에 따른 「전기설비기준」이 정하는 바에 의하고, 감지기회로 및 부속회로의 전로와 대지 사이 및 배선 상호간의 절연저항은 1경계구역마다 ( ③ )를 사용하여 측정한 절연저항이 ( ④ ) 이상이 되도록 할 것
+ㆍ자동화재탐지설비의 감지기회로의 전로저항은 ( ⑤ ) 이하가 되도록 해야 하며, 수신기의 각 회로별 종단에 설치되는 감지기에 접속되는 배선의 전압은 감지기 정격전압의 80[%] 이상이어야 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 전자파
+② 송배선식
+③ 직류 250[V]의 절연저항측정기
+④ 0.1[㏁]
+⑤ 50[Ω]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>그림은 Y-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Δ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기동에 대한 시퀀스회로도이다. 회로를 보고 다음 각 물음에 답하시오.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>가) Y-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 기동회로를 사용하는 이유를 쓰시오.
+나) Y-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 운전이 가능하도록 보조회로(제어회로)에서 기호 ① 부분의 접점 명칭을 쓰시오.
+다) 기호 ②, ③의 접점 기호를 그리시오.
+라) Y-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 운전이 가능하도록 주회로 부분을 미완성 도면에 완성하시오.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 기동전류를 작게 하기 위하여
+나) 한시동작 b접점
+다) 그림 참조
+라) 그림 참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물 내부에 가압송수장치로서 기동용 수압개폐장치를 사용하는 옥내소화전함과 P형 발신기 세트를 다음과 같이 설치하였다. 다음 각 물음에 답하시오. (단 경종선에는 단락보호장치를 하고, 각 배선상에 다른 층의 화재통보에 지장이 없도록 유효한 조치를 하였다. 또한, 전화선은 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) ①~④의 전선가닥수를 답란에 쓰시오.
+나) 설치된 P형 수신기는 몇 회로용인가?
+다) 5층 경종선이 단락되었을 때 경보하여야 하는 층은?
+라) 발신기에 부착되는 음향장치에 대하여 다음 항목에 답하시오.
+ - 정격전압의 (   )[%] 전압에서 음향을 발할 수 있는 것으로 할 것
+ - 음량의 성능 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) ①10가닥, ②12가닥, ③14가닥, ④18가닥
+나) 25회로용
+다) 1층, 2층, 3층, 4층, 6층
+라) 
+ - 80[%]
+ - 음량의 성능 : 부착된 음향장치의 중심에서 1[m] 위치에서 90[dB] 이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비 및 시각경보장치의 화재안전기술기준에서 감지기의 설치제외장소에 관한 다음 (  )안을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ천장 또는 반자의 높이가 ( ① )[m] 이상인 장소. 다만, 감지기로서 부착높이에 따라 적응성이 있는 장소는 제외한다.
+ㆍ헛간 등 외부와 기류가 통하는 장소로서 감지기에 따라 ( ② )을 유효하게 감지할 수 없는 장소
+ㆍ( ③ )가 체류하고 있는 장소
+ㆍ고온도 및 ( ④ )로서 감지기의 기능이 정지되기 쉽거나 감지기의 유지관리가 어려운 장소
+ㆍ목욕실ㆍ욕조나 샤워시설이 있는 화장실ㆍ기타 이와 유사한 장소
+ㆍ파이프덕트 등 그 밖의 이와 비슷한 것으로서 ( ⑤ )층마다 방화구획된 것이나 수평단면적이 ( ⑥ )[m²] 이하인 것
+ㆍ먼지ㆍ가루 또는 ( ⑦ )가 다량으로 체류하는 장소 또는 주방 등 평상시 연기가 발생하는 장소 (단, 연기감지기에 한한다.)
+ㆍ프레스공장ㆍ주조공장 등 ( ⑧ )로서 감지기의 유지관리가 어려운 장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 20
+② 화재발생
+③ 부식성 가스
+④ 저온도
+⑤ 2개
+⑥ 5
+⑦ 수증기
+⑧ 화재발생의 위험이 적은 장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이산화탄소 소화설비의 음향경보장치 설치기준에 대한 설명이다. (  ) 안에 알맞은 말을 넣으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ( ① )를 설치한 것은 그 기동장치의 조작과정에서, ( ② )를 설치한 것은 ( ③ )와 연동하여 자동으로 경보를 발하는 것으로 할 것
+ㆍ소화약제의 방출개시 후 ( ④ )분 이상 경보를 계속할 수 있는 것으로 할 것
+ㆍ방호구역 또는 방호대상물이 있는 구획 안에 잇는 자에게 유효하게 경보할 수 있는 것으로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 수동식 기동장치
+② 자동식 기동장치
+③ 화재감지기
+④ 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경보설비에 대한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 경보설비의 정의를 쓰시오.
+나) 경보설비의 종류 6가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 화재발생 사실을 통호하는 기계ㆍ기구 또는 설비
+나) 
+ ① 자동화재탐지설비
+ ② 시각경보기
+ ③ 자동화재속보설비
+ ④ 누전경보기
+ ⑤ 가스누설경보기
+ ⑥ 비상방송설비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230304a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230307a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230310a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230314(1</t>
+  </si>
+  <si>
+    <t>230314a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230315a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2374,13 +2738,26 @@
       <name val="Cambria Math"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2397,7 +2774,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2411,6 +2788,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -5062,10 +5442,10 @@
       <c r="C2" s="4">
         <v>5</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>230201</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>359</v>
       </c>
       <c r="F2" s="4"/>
@@ -5080,10 +5460,10 @@
       <c r="C3" s="4">
         <v>4</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>230202</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>358</v>
       </c>
       <c r="F3" s="4"/>
@@ -5096,10 +5476,10 @@
       <c r="C4" s="4">
         <v>5</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>230203</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>360</v>
       </c>
       <c r="F4" s="4"/>
@@ -5321,6 +5701,307 @@
       </c>
       <c r="F19" s="4" t="s">
         <v>380</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2126D612-9595-4040-BF2E-27D166DD1870}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="49.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="11" style="4" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C2" s="4">
+        <v>6</v>
+      </c>
+      <c r="D2" s="6">
+        <v>230301</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C4" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C5" s="4">
+        <v>4</v>
+      </c>
+      <c r="D5" s="6">
+        <v>230304</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C6" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" s="4">
+        <v>3</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C8" s="4">
+        <v>6</v>
+      </c>
+      <c r="D8" s="6">
+        <v>230307</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C9" s="4">
+        <v>6</v>
+      </c>
+      <c r="D9" s="6">
+        <v>230308</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" s="4">
+        <v>6</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="F10" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C11" s="4">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4">
+        <v>230310</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C12" s="4">
+        <v>6</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C13" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="261" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C14" s="4">
+        <v>5</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C15" s="4">
+        <v>7</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C16" s="4">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="261" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C17" s="4">
+        <v>8</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C18" s="4">
+        <v>4</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C19" s="4">
+        <v>3</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="842" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C2EA8C6-CD8F-4F77-B751-14E6DDAFA40E}"/>
+  <xr:revisionPtr revIDLastSave="845" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B94D4262-E2CB-43CB-B80B-F6EAE410C3A9}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="8" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="24년 3회" sheetId="7" r:id="rId6"/>
     <sheet name="23년 1회" sheetId="8" r:id="rId7"/>
     <sheet name="23년 2회" sheetId="9" r:id="rId8"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId9"/>
+    <sheet name="23년 3회" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2672,14 +2672,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>230314(1</t>
-  </si>
-  <si>
     <t>230314a</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>230315a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230314(1, 230314(2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2774,7 +2775,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2791,9 +2792,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5750,10 +5748,9 @@
       <c r="C2" s="4">
         <v>6</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="4">
         <v>230301</v>
       </c>
-      <c r="E2" s="6"/>
       <c r="F2" s="4" t="s">
         <v>382</v>
       </c>
@@ -5787,10 +5784,10 @@
       <c r="C5" s="4">
         <v>4</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>230304</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>423</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -5829,10 +5826,10 @@
       <c r="C8" s="4">
         <v>6</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>230307</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>424</v>
       </c>
     </row>
@@ -5843,7 +5840,7 @@
       <c r="C9" s="4">
         <v>6</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>230308</v>
       </c>
       <c r="F9" s="4" t="s">
@@ -5860,7 +5857,6 @@
       <c r="C10" s="4">
         <v>6</v>
       </c>
-      <c r="D10" s="6"/>
       <c r="F10" s="4" t="s">
         <v>397</v>
       </c>
@@ -5878,7 +5874,7 @@
       <c r="D11" s="4">
         <v>230310</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="4" t="s">
         <v>425</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -5935,10 +5931,10 @@
         <v>7</v>
       </c>
       <c r="D15" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>427</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>409</v>
@@ -5954,9 +5950,11 @@
       <c r="C16" s="4">
         <v>9</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6" t="s">
-        <v>428</v>
+      <c r="D16" s="5">
+        <v>230315</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>427</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>412</v>

--- a/소방설비기사_실기_문제은행.xlsx
+++ b/소방설비기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7c0279c9e9ffeec/Desktop/Web_CBT_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="845" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B94D4262-E2CB-43CB-B80B-F6EAE410C3A9}"/>
+  <xr:revisionPtr revIDLastSave="1206" documentId="13_ncr:1_{BE96BAE2-30E9-426D-A6AB-4D58FC00907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F682BD8-AA0F-4E06-8CBA-CDAF1AF06CFF}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="8" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="11" xr2:uid="{57070AA3-38A7-403F-B980-3B2EE621CAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="25년 1회" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,10 @@
     <sheet name="23년 1회" sheetId="8" r:id="rId7"/>
     <sheet name="23년 2회" sheetId="9" r:id="rId8"/>
     <sheet name="23년 3회" sheetId="10" r:id="rId9"/>
+    <sheet name="22년 1회" sheetId="11" r:id="rId10"/>
+    <sheet name="22년 2회" sheetId="12" r:id="rId11"/>
+    <sheet name="22년 3회" sheetId="14" r:id="rId12"/>
+    <sheet name="21년 1회" sheetId="15" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="552">
   <si>
     <t>문제</t>
   </si>
@@ -2681,6 +2685,662 @@
   </si>
   <si>
     <t>230314(1, 230314(2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상콘센트설비에 대한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가) 전원회로의 종류, 전압 및 그 공급용량을 쓰시오.
+나) 전원으로부터 각 층의 비상콘센트에 분기되는 경우에 보호함 안에 설치하여야 하는 기구를 쓰시오.
+다) 비상콘센트설비 배선의 설치기준에서 전원회로의 배선과 그 밖의 배선 종류에 대해 쓰시오.
+ - 전원회로의 배선 :
+ - 그 밖의 배선 : </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 
+ - 종류 : 단상교류
+ - 전압 : 220[V]
+ - 공급용량 : 1.5[kVA] 이상
+나) 분기배선용 차단기
+다) 
+ - 전원회로의 배선 : 내화배선
+ - 그 밖의 배선 : 내화배선 또는 내열배선(2가지 다 작성)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방시설용 비상전원수전설비의 화재안전기준에서 큐비클형의 설치기준에 관한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) ( ① ) 큐비클 또는 공용 큐비클식으로 설치할 것
+나) 외함의 두께 ( ② )[mm] 이상의 강판과 이와 동등 이상의 강도와 ( ③ )이 있는 것으로 제작하여야 하며, 개구부에는 ( ④ )방화문 또는 ( ⑤ )방화문을 설치할 것
+다) 외함의 바닥에서 ( ⑥ )[cm] (시험단자, 단자대 등의 충전부는 ( ⑦ )[cm]) 이상의 높이에 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 전용
+② 2.3[mm]
+③ 내화성능
+④ 60분+방화문, 60분(2가지 다 작성)
+⑤ 30분
+⑥ 10[cm]
+⑦ 15[cm]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누전경보기의 화재안전기준과 형식승인 및 제품검사의 기술기준을 참고하여 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가) 공칭작동전류치는 몇 [mA] 이하인가?
+나) 감도조정장치를 갖는 누전경보기의 최대치는 몇 [A] 이하인가?
+다) 변류기의 1차 권선과 2차 권선 간의 절연저항측정에 사용되는측정기구와 측정된 절연저항의 양부에 대한 기준을 쓰시오.
+ - 측정기구 : 
+ - 양부 판단기준 : </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 200[mA]
+나) 1[A] 이하
+다) 
+ - 측정기구 : 직류 500[V] 절연저항계
+ - 양부 판단기준 : 5[㏁] 이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비를 설치하여야 할 특정소방대상물(연면적, 바닥면적 등의 기준)에 대한 다음(  )안을 완성하시오. (단, 전부 필요한 경우는 '전부'라고 쓰고, 필요 없는 경우에는 '필요 없음'이라고 답할 것)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상방송설비에 사용되는 용어의 정의를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 소리를 크게 하여 멀리까지 전달될 수 있도록 하는 장치로서 일명 스피커를 말한다.
+나) 가변저항을 이용하여 전류를 변화시켜 음량을 크게 하거나 작게 조절할 수 있는 장치를 말한다.
+다) 전압ㆍ전류의 직폭을 늘려 감도를 좋게 하고 미약한 음성전류를 커다란 음성전류로 변화시켜 소리를 크게 하는 장치를 말한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 확성기
+나) 음량조절기
+다) 증폭기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상방송설비의 확성기(speaker)회로에 음량조정기를 설치하고자 한다. 미완성 결선도를 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도면은 준비작동식 스프링클러설비에 사용되는 Super Visory Panel에서 수신기까지의 내부결선도이다. 다음 도면을 완성시키고 ①~⑧에 이용되는 전선의 용도에 관한 명칭을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 전원 -
+② 전원+
+③ 밸브개방 확인
+④ 밸브기동
+⑤ 밸브주의
+⑥ 입력스위치
+⑦ 댐퍼스위치
+⑧ 솔레노이드 밸브</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가요전선관공사에서 다음에 사용되는 재료의 명칭은 무엇인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 가요전선관과 박스의 연결 :
+나) 가요전선관과 금속관의 연결 : 
+다) 가요전선관과 가요전선관의 연결 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 스트레이트박스 커넥터
+나) 콤비네이션 커플링
+다) 스플리트 커플링</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 회로에서 램프 L의 작동을 주어진 타임차트에 표시하고, 각 회로에 대한 논리회로를 그리시오.(단, PB : 누름버튼스위치, LS : 리미트스위치, X : 릴레이)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제연설비의 수신반에서 100[m] 떨어진 장소의 감지기가 작동할 때 소비된 전류가 1[A]라고 한다. 이때의 전압강하[V]를 구하시오. (단, 전선굵기는 1.5[mm]이며 단상 2선식을 사용한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 옥내소화전설비를 겸용한 자동화재탐지설비의 계통도이다. 기호 ㉮ ~ ㉲의 최소 전선가닥수를 쓰시오. (단, 옥내소화전은 기동용 수압개폐장치를 이용하느 방식을 채택하였다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 수신기
+나) 제어반
+다) 부수신기
+라) 표시반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>길이 18[m]의 통로에 객석유도등을 설치하려고 한다. 이때 필요한 객석유도등의 수량은 최소 몇 개인지 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(18/4)-1 = 3.5 =4개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 수신기와 감지기 사이에 설치(단, 순시기에서 도통시험을 하지 않을 때)
+② 조작 및 점검에 편리하고 화재 및 침수 등의 재해로 인한 피해를 받을 우려가 없는 장소에 설치
+③ 전원입력측에 과전류차단기 설치(수신기를 거쳐 전원공급이 안 될 경우)하고 전원이 정전이 즉시 수신기에 표시되도록 할 것. 사용전원 및 예비전원의 시험을 할 수 있을 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림과 같은 건물평도의 경우 자동화재탐지설비의 최소경계구역의 수를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음과 같은 장소에 차동식 스포트형 감지기 2종을 설치하는 경우와 광전식 스포트형 2종을 설치하는 경우 최소 감지기 소요개수를 산정하시오. (단, 주요구조부는 내화구조, 감지기의 설치높이는 3[m] 이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 차동식 스포트형 감지기(2종) 소요개수
+나) 광전식 스포트형 감지기(2종) 소요개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P형 수신기의 예비전원을 시험하는 방법과 양부판단의 기준에 대하여 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ 시험방법 : 상용전원 및 비상전원이 사고 등으로 정전된 경우, 자동적으로 예비전원으로 절환되며, 또한 정전복구시에 자동적으로 상용전원으로 절환되는지의 여부를 다음에 따라 확인
+① 예비전원시험 스위치를 누름
+② 전압계의 지시치가 지정범위 내에 있는지 확인
+③ 상용전원을 차단하고 자동절환릴레이의 작동상황 조사
+ㆍ양부판단의 기준 : 예비전원의 전압, 용량, 절환상황 및 복구작동이 정상일 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상방송설비의 설치기준에 관한 다음 (  )안을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 확성기의 음성입력은 실내에 설치하는 것에 있어서는 ( ① )[W] 이상일 것
+나) 확성기는 각 층마다 설치하되, 그 층의 각 부분으로부터 하나의 확성기까지 수평거리가 ( ② )[m] 이하가 되도록 하고, 해당 층의 각 부분에 유효하게 정보를 발할 수 있도록 설치할 것
+다) 음량조정기를 설치하는 경우 음량조정기의 배선은 ( ③ )선식으로 할 것
+라) 조작부의 조작스위치는 바닥으로부터 ( ④ )[m] 이상 ( ⑤ )[m] 이하의 높이에 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 1
+② 25
+③ 3
+④ 0.8
+⑤ 1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유량 2400[L/min], 양정 100[m]인 스프링클러설비용 펌프전동기의 용량을 계산하시오. (단, 효율 : 75[%], 전달계수 : 1.1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15[kW] 스프링클러펌프용 유도전동기가 있다. 전동기의 역률이 85[%]일 때, 역률을 95[%]로 개선할 수 있는 전력용 콘덴서일 경우 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 콘덴서의 용량[kVar]을 구하시오.
+나) 역률 개선 전 전동기의 무효전력[kVar]을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 감지기가 그림과 같이 배치되어 있을 때 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 위의 도면을 보고 배관에 가닥수를 표시하시오.
+나) 위의 도면을 보고 실제 배선도를 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P형 수신기와 감지기와의 배선회로에서 종단저항은 11[㏀], 배선저항은 50[Ω], 릴레이저항은 700[Ω]이며, 회로전압이 DC 24[V]일 때 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감지기회로의 배선에서 교차회로방식의 적용설비 5가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 분말소화설비
+② 할론소화설비
+③ 이산화탄소 소화설비
+④ 준비작동식 스프링클러설비
+⑤ 일제살수식 스프링클러설비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 옥내소화전설비 감시제어반의 기능에 대한 적합기준이다. (  ) 안을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 각 펌프의 작동여부를 확인할 수 있는 ( ① ) 및 ( ② ) 기능이 있어야 할 것
+나) 수조 또는 물올림수조가 ( ③ )로 될 때 표시등 및 음향으로 경보할 것
+다) 각 확인회로(기동용 수압개폐장치의 압력스위치회로ㆍ수조 또는 물올림수조의 저수위감시회로ㆍ급수배관에 설치되어 있는 개폐밸브의 폐쇄상태 확인회로를 말한다)마다 ( ④ )시험 및 ( ⑤ )시험을 할 수 있어야 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수신기에서 60[m] 떨어진 장소의 감지기가 작동할 때 소비된 전류가 0.8[A]라고 한다. 이때의 전압강하[V]를 구하시오. (단, 전선굵기는 1.5[mm]이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물 내부에 가압송수장치를 기동용 수압개폐장치로 사용하는 옥내소화전함과 P형 발신기세트를 다음과 같이 설치하였다. 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) ㉮~㉳의 최소 전선가닥수를 쓰시오.
+나) 자동화재탐지설비의 배선설치기준에 관한 다음 (  ) 안을 완성하시오.
+ - 자동화재탐지설비의 감지기회로의 전로저항은 ( ① )[Ω] 이하가 되도록 해야 하며, 수신기의 각 회로별 종단에 설치되는 감지기에 접속되는 배선의 전압은 감지기 정격전압의 ( ② )]%] 이상이어야 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 
+㉮ 8가닥
+㉯ 8가닥
+㉰ 14가닥
+㉱ 19가닥
+㉲ 10가닥
+㉳ 8가닥
+나) 
+① 50
+② 80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스프링클러설비에는 제어반을 설치하되, 감시제어반과 동력제어반으로 구분하여 설치하지 아니할 수 있는 겨우 다음 (  ) 안을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 다음의 어느 하나에 해당하지 않는 특정소방대상물에 설치되는 스프링클러설비
+ - 지하층을 제외한 층수가 ( ① )층 이상으로서 연면적이 ( ② )[m²] 이상인 것
+ - 위에 해당하지 않는 특정소방대상물로서 지하층의 바닥면적의 합계가 ( ③ )[m²] 이상인 것
+나) ( ④ )에 따른 가압송수장치를 사용하는 경우
+다) ( ⑤ )에 따른 가압송수장치를 사용하는 경우
+라) ( ⑥ )에 따른 가압송수장치를 사용하는 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 7
+② 2000
+③ 3000
+④ 내연기관
+⑤ 고가수조
+⑥ 가압수조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감지기회로의 도통시험을 위한 종단저항의 설치기준 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 점검 및 관리가 쉬운 장소에 설치할 것
+② 전용함 설치시 바닥에는 1.5[m] 이내의 높이에 설치
+③ 감지기회로의 끝부분에 설치하며, 종단감지기에 설치시 구별이 쉽도록 해당 감지기의 기판 및 감지기 외부등에 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주어진 진리표를 보고 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 가장 간략화된 논리식으로 표현하시오.
+ - Y1
+ - Y2
+나) 가)의 논리식을 무접점회로로 그리시오.
+다) 가)의 논리식을 유접점회로로 그리시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 다음과 같이 주어진 기구를 이용하여 제어회로부분의 미완성 회로를 완성하시오. (단, PB_on을 누르면 MC가 여자되고 자기유지되며, PB_off를 누르면 MC가 소자되고 기구의 개수 및 접점 등은 최소개수를 사용하도록 한다.)
+나) 49는 어떤 경우에 작동하지는 2가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 그림 참조
+나)
+① 전동기에 과부하가 걸릴 때
+② 전류조정 다이얼 세팅치에 적정 전류보다 낮게 세팅했을 때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유도등 및 비상조명등에 관한 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 축전지
+나) ① 20, ② 60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 유도등의 비상전원은?
+나) 비상조명등의 설치기준에 관한 다음 (  )안을 완성하시오.
+ - 비상조명등의 비상전원은 비상조명등을 ( ① )분 이상 유효하게 작동시킬 수 있는 용량으로 할 것. 다만, 다음의 특정소방대상물의 경우에는 그 부분에서 피난층에 이르는 부분의 비상조명등을 ( ② )분 이상 유효하게 작동시킬 수 있는 용량으로 하여야 한다.
+ ㆍ지하층을 제외한 층수가 11층 이상의 층
+ ㆍ지하층 또는 무창층으로서 용도가 도매시장ㆍ소매시장ㆍ여객자동차터미널 지하역사 또는 지하상가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림은 10개의 접점을 가진 스위칭회로이다. 이 회로의 접점수를 최소화하여 스위칭회로를 그리시오. (단, 주어진 스위칭회로의 논리식을 최소화하는 과정을 모두 기술하고 최소화된 스위칭회로를 그리도록 한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가) 논리식 :
+나) 최소화한 스위칭회로 : </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상용 조명부하에 연축전지를 설치하고자 한다. 주어진 조건과 표, 그림을 참고하여 연축전지의 용량 [Ah]을 구하시오. (단, 2016년 건축전기설비 설계기준에 의할 것)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방용 케이블과 다른 용도의 케이블을 배선전용실에 함께 배선할 때 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 소방용 케이블을 내화성능을 갖는 배선전용실 등의 내부에 소방용이 아닌 케이블과 함께 노출하여 배선할 때 소방용 케이블과 다른 용도의 케이블간의 피복과 피복간의 이격거리는 몇 cm 이상이어야 하는지 쓰시오.
+나) 부득이하여 가)와 같이 이격시킬 수 없어 불연성 격벽을 설치한 경우에 격벽의 높이는 굵은 케이블 지름의 몇 배 이상이어야 하는지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 15[cm]
+나 1.5배</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도면은 할로겐화합물 소화설비의 수동족작함에서 할론제어반까지의 결선도이다. 주어진 도면과 조건을 이용하여 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) ①~⑦의 전선의 명칭을 쓰시오. (단, 전선의 가닥수는 최소가닥수로 한며, 복구스위치 및 도어스위치는 없는 것으로 한다.)
+나) 기호 ②, ③의 전선의 최소굵기는[mm²]는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 
+① 기동스위치 또는 방출지연스위치
+② 전원-
+③ 전원+
+④ 방출표시등
+⑤ 사이렌
+⑥ 감지기 A
+⑦ 감지기 B
+나) 2.5[mm²]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 도면은 할론소화설비와 연동하는 감지기 설비를 나타낸 그림이다. 조건을 참조하여 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조건]
+① 연기감지기 4개를 설치한다. 수동조작함 1개, 사이렌 1개, 방출표시등 1개, 종단저항 2개를 표시한다.
+② 사용하는 전선은 후강전선관이며, 콘크리트 매입으로 한다.
+③ 기동을 만족시키는 최소의 배선을 하도록 한다.
+④ 건축물은 내화구조로 각 층의 높이는 3.8[m]이다.
+[문제]
+가) 평면도를 완성하시오.
+나) 수신반과 수동조작함 사이의 배선 명칭을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 그림 참조
+나) 전원 +, -, 방출지연스위치, 감지기 AㆍB, 기동스위치, 방출표시등, 사이렌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 이산화탄소 소화설비의 간선계통이다. 각 물음에 답하시오. (단, 감지기공통선과 전원공통선은 각각 분리해서 사용하는 조건이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) ㉮~㉸까지의 배선 가닥수를 쓰시오.
+나) ㉲의 배선별 용도를 쓰시오. (단, 해당 배선 가닥수까지만 끼록)
+다) ㉸의 배선 중 ㉲의 배선과 병렬로 접속하지 않고 추가해야 하는 배선의 용도는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유도등의 비상전원 설치기준에 관한 다음 (  )안을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유도등 ( ① )분 이상 유효하게 작동시킬 수 있는 용량으로 할 것. 다만, 다음의 특정 소방대상물의 경우에는 그 부분에서 피난층에 이르는 부분의 유도등을 ( ② )분 이상 유효하게 작동시킬 수 있는 용량으로 하여야 한다.
+ ㆍ지하층을 제외한 층수가 ( ③ )층 이상의 층
+ ㆍ지하층ㆍ무창층으로 도매시장ㆍ소매시장ㆍ여객자동차터미널ㆍ지하철역사ㆍ지하상가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 20
+② 60
+③ 11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3상 380[V], 30[kW] 스프링클러펌프용 유도전동기가 있다. 전동기의 역률 60[%]일 때, 역률을 90[%]로 개선할 수 있는 전력용 콘덴서의 욜양은 몇 [kVA]이겠는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림과 같이 구획된 철근콘크리트 건물의 공장이 있따. 다음 표에 따라 자동화재탐지설비의 감지기를 설치하고자 한다. 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 다음 표를 완성하여 감지기 개수를 선정하시오.
+나) 해당 구역에 감지기를 배치하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 그림과 같이 지하 1층에서 지상 5층까지 각 층의 평면이 동일하게, 각 층의 높이가 4[m]인 학원건물에 자동화재탐지설비를 설치한 경우이다. 다음 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 하나의 층에 대한 자동화재탐지설비의 수평경계구역수를 구하시오.
+나) 본 소방대상물 자동화재탐지설비의 수직 및 수평경계구역수를 구하시오.
+ ① 수평경계구역
+ ② 수직경계구역
+다) 계단감지기는 각각 몇 층에 설치해야 하는지 쓰시오.
+라) 엘리베이터 권상기실 상부에 설치해야 하는 감지기의 종류를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 PB_on 동작시 X 릴레이가 동작하고 특정 시간 세팅 후 타이머가 동작하여 MC가 동작하는 시퀀스회로도이다. PB_on을 동작시킨 후 X 릴레이와 타이머가 소자되어도 MC가 동작하도록 시퀀스를 수정하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무선통신보조설비에 사용되는 무반사 종단저항의 설치목적을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전송로로 전송되는 전자파가 전송로의 종단에서 반사되어 교신을 방해하는 것을 막기 위함이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음과 같이 총 길이가 2800[m]인 터널에 자동화재탐지설비를 설치하는 경우 다음 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 최소경계구역은 몇 개로 구분해야 하는지 계산하시오.
+나) 다음 (   )안에 알맞은 말을 쓰시오.
+ - 감지기의 작동에 의하여 다른 소방시설 등이 연동되는 경우로서 해당 소방시설 등의 작동을 위한 정확한 (  )를(을) 확인할 필요가 있는 경우에는 경계구역의 길이가 해당 설비의 방호구역 등에 포함되도록 설치하여야 한다.
+다) 터널에 설치할 수 있는 감지기의 종류 3가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 2800/100 = 28개
+나) 발화위치
+다) 
+ ① 차동식 분포형 감지기
+ ② 정온식 감지선형 감지기(아날로그식)
+ ③ 중앙기술심의위원회의 심의를 거쳐 터널화재에 적응성이 있다고 인정된 감지기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음과 같은 조건을 참고하여 배선도로 나타내시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[조건]
+① 배선 : 천장은폐배선
+② 전력선 : 4가닥, 450/750[V] 저독성 난연 가교폴리올레핀 절연전선 1.5[mm²]
+③ 전선관 : 후강전선관 22[mm]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비 및 시각경보장치의 화재안전기술기준(NFTC 203)에서 자동화재탐지설비의 음향장치의 설치기준에관한 사항이다. 다음 (  )안을 완성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>층수가 ( ① )층[공동주택의 경우에는 ( ② )층] 이상의 특정소방대상물은 다음의 기준에 따라 정보를 발할 수 있도록 할 것
+ ㆍ 발화층 / 경보층
+ - 2층 이상 발화 / ( ③ )
+ - 1층 발화 / ( ④ )
+ - 지하층 발화 / ( ⑤ )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 11
+② 16
+③ 발화층, 직상 4개층
+④ 발화층, 직상 4개층, 지하층
+⑤ 발화층, 직상층, 기타의 지하층</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어느 특정소방대상물에 자동화재탐지설비용 공기관식 차동식 분포형 감지기를 설치하려고 한다. 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 공기관의 노출부분은 감지구역마다 몇 [m] 이상으로 하여야 하는가?
+나) 하나의 검출부에 접속하는 공기관의 길이는 몇 [m] 이하로 하여야 하는가?
+다) 공기관과 감지구역의 각 변과의 수평거리는 몇 [m] 이하이어야 하는가?
+라) 공기관 상호간의 거리는 몇 [m] 이하이어야 하는가? (단, 주요구조부가 비내화구조이다.)
+마) 공기관의 두께와 바깥지름은 각각 몇 [mm] 이상인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 20[m]
+나) 100[m]
+다) 1.5[m]
+라) 6[m]
+마) 두께 : 0.3[mm], 바깥지름 : 1.9[mm]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220104a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220107a</t>
+  </si>
+  <si>
+    <t>220110a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220111a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220114, 220114(1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220114a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220115a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220116a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220201a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220202a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220207a(1, 220207a(2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220207(1,
+220207(2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 사이렌
+나) 비상벨
+다) 정온식 스포트형 감지기
+라) 차동식 스포트형 감지기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220213a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220216a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220217a(1, 220217a(2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220301a</t>
+  </si>
+  <si>
+    <t>220302a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220304a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220305a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유량 3000[Lpm], 양정 80[m]인 스프링클러설비용 펌프 전동기의 용량을 계산하시오. (단, 효율 : 0.7, 전달계수 : 1.15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000Lpm = 3m³/min = 3m³/60s(1000L=1m³, 1min=60s)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220306a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220311(1, 220311(2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220311a(1, 220311a(2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220312a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220313a</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2775,7 +3435,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2793,6 +3453,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3665,6 +4331,1231 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BED9CA1B-0D7B-4F63-A0A6-7CAB13B5087A}">
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="49.59765625" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C2" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C3" s="4">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C4" s="4">
+        <v>6</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4">
+        <v>5</v>
+      </c>
+      <c r="D5" s="6">
+        <v>220104</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4">
+        <v>5</v>
+      </c>
+      <c r="D6" s="6">
+        <v>220105</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C7" s="4">
+        <v>5</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4">
+        <v>5</v>
+      </c>
+      <c r="D8" s="7">
+        <v>220107</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C9" s="4">
+        <v>12</v>
+      </c>
+      <c r="D9" s="7">
+        <v>220108</v>
+      </c>
+      <c r="E9" s="7">
+        <v>220108</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C10" s="4">
+        <v>5</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="1" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="4">
+        <v>6</v>
+      </c>
+      <c r="D11" s="7">
+        <v>220110</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4">
+        <v>5</v>
+      </c>
+      <c r="D12" s="6">
+        <v>220111</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4">
+        <v>4</v>
+      </c>
+      <c r="D13" s="6">
+        <v>220112</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="4">
+        <v>5</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4">
+        <v>5</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4">
+        <v>6</v>
+      </c>
+      <c r="D16" s="6">
+        <v>220115</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C17" s="4">
+        <v>4</v>
+      </c>
+      <c r="D17" s="6">
+        <v>220116</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C18" s="4">
+        <v>4</v>
+      </c>
+      <c r="D18" s="6">
+        <v>220117</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C19" s="4">
+        <v>6</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12AD294D-8CA0-4FA8-9001-70245DAE3D65}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="49.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="11" style="4" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="C2" s="4">
+        <v>6</v>
+      </c>
+      <c r="D2" s="6">
+        <v>220201</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C3" s="4">
+        <v>6</v>
+      </c>
+      <c r="D3" s="6">
+        <v>220202</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C4" s="4">
+        <v>6</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C5" s="4">
+        <v>5</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C6" s="4">
+        <v>4</v>
+      </c>
+      <c r="D6" s="6">
+        <v>220205</v>
+      </c>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C7" s="4">
+        <v>6</v>
+      </c>
+      <c r="D7" s="6">
+        <v>220206</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="C8" s="4">
+        <v>5</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="C9" s="4">
+        <v>4</v>
+      </c>
+      <c r="D9" s="6">
+        <v>220116</v>
+      </c>
+      <c r="E9" s="6">
+        <v>220208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="C10" s="4">
+        <v>4</v>
+      </c>
+      <c r="D10" s="6">
+        <v>220209</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="C11" s="4">
+        <v>5</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="4">
+        <v>5</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C13" s="4">
+        <v>5</v>
+      </c>
+      <c r="D13" s="6">
+        <v>220212</v>
+      </c>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C14" s="4">
+        <v>9</v>
+      </c>
+      <c r="D14" s="6">
+        <v>220213</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C15" s="4">
+        <v>6</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C16" s="4">
+        <v>6</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C17" s="4">
+        <v>8</v>
+      </c>
+      <c r="D17" s="6">
+        <v>220216</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C18" s="4">
+        <v>6</v>
+      </c>
+      <c r="D18" s="6">
+        <v>220217</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C19" s="4">
+        <v>4</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3023BB7-500D-403C-8665-B061CE199642}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="49.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="11" style="4" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C2" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2" s="6">
+        <v>220301</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C3" s="4">
+        <v>4</v>
+      </c>
+      <c r="D3" s="6">
+        <v>220302</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C4" s="4">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6">
+        <v>220303</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="C5" s="4">
+        <v>6</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="C6" s="4">
+        <v>7</v>
+      </c>
+      <c r="D6" s="6">
+        <v>220305</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C7" s="4">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6">
+        <v>220306</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C8" s="4">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6">
+        <v>220307</v>
+      </c>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4">
+        <v>6</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="C10" s="4">
+        <v>3</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C11" s="4">
+        <v>4</v>
+      </c>
+      <c r="D11" s="6">
+        <v>220310</v>
+      </c>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C12" s="4">
+        <v>10</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C13" s="4">
+        <v>7</v>
+      </c>
+      <c r="D13" s="6">
+        <v>220312</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C14" s="4">
+        <v>5</v>
+      </c>
+      <c r="D14" s="6">
+        <v>220313</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C15" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C16" s="4">
+        <v>5</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="C17" s="4">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C18" s="4">
+        <v>5</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C19" s="4">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>523</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81EB656D-594B-41E6-B307-403378C75E71}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="49.59765625" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="52.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F4D140-F625-46C7-BF54-7660D0FA16E6}">
   <dimension ref="A1:F19"/>
